--- a/VERGARA/Mayo/vergara MAYO.xlsx
+++ b/VERGARA/Mayo/vergara MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECFB1E8-F112-49D4-8D6C-F4F5F6E05441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73534D49-ACAF-4E70-B8CD-FEB8EAFE16F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$Q$101</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$108</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="290">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -891,6 +891,12 @@
   </si>
   <si>
     <t>Matafuegos Firex 5 kg</t>
+  </si>
+  <si>
+    <t>Zaffalon Veronica -por guardia de vaciamiento de agua de napa con urgencia debido a un corte de luz que tuvo el consorcio se instalaron dos bombas para ayudar a la bomba original a- Se asiste con bombas propias y personal para su vaciado</t>
+  </si>
+  <si>
+    <t>Transf 21/05</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1505,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1738,6 +1744,15 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="20" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1760,6 +1775,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1836,14 +1857,11 @@
     <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2211,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -2269,12 +2287,12 @@
       <c r="A5" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="169" t="s">
+      <c r="B5" s="174" t="s">
         <v>275</v>
       </c>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="170"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="175"/>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
@@ -2288,49 +2306,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="172" t="s">
+      <c r="B8" s="177" t="s">
         <v>274</v>
       </c>
-      <c r="C8" s="172"/>
+      <c r="C8" s="177"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="172"/>
-      <c r="C9" s="172"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="177"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="172"/>
-      <c r="C10" s="172"/>
+      <c r="B10" s="177"/>
+      <c r="C10" s="177"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="171" t="s">
+      <c r="A13" s="176" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="171"/>
-      <c r="D13" s="171"/>
-      <c r="E13" s="171"/>
+      <c r="B13" s="176"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
+      <c r="A14" s="176"/>
+      <c r="B14" s="176"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="176"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="171"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
+      <c r="A15" s="176"/>
+      <c r="B15" s="176"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="171"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
+      <c r="A16" s="176"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+      <c r="E16" s="176"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2426,10 +2444,10 @@
       <c r="E27" s="96"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="167" t="s">
+      <c r="A28" s="172" t="s">
         <v>276</v>
       </c>
-      <c r="B28" s="168"/>
+      <c r="B28" s="173"/>
       <c r="C28" s="5"/>
       <c r="D28" s="126">
         <v>31000</v>
@@ -2439,10 +2457,10 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="167" t="s">
+      <c r="A29" s="172" t="s">
         <v>278</v>
       </c>
-      <c r="B29" s="168"/>
+      <c r="B29" s="173"/>
       <c r="C29" s="5"/>
       <c r="D29" s="126">
         <v>470000</v>
@@ -2473,92 +2491,84 @@
       <c r="E31" s="67"/>
     </row>
     <row r="32" spans="1:7" s="40" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="167" t="s">
+      <c r="A32" s="172" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="168"/>
+      <c r="B32" s="173"/>
       <c r="C32" s="54"/>
       <c r="D32" s="138">
         <v>226692</v>
       </c>
       <c r="E32" s="122"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="167" t="s">
+    <row r="33" spans="1:7" s="40" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="208"/>
+      <c r="B33" s="171"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="207">
+        <v>70868</v>
+      </c>
+      <c r="E33" s="122"/>
+    </row>
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="172" t="s">
         <v>220</v>
       </c>
-      <c r="B33" s="168"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="127">
+      <c r="B34" s="173"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="127">
         <v>719.9</v>
       </c>
-      <c r="E33" s="122"/>
-    </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="26" t="s">
+      <c r="E34" s="122"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="99">
-        <f>SUM(D32:D33)</f>
-        <v>227411.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="33" t="s">
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="99">
+        <f>SUM(D32:D34)</f>
+        <v>298279.90000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="100"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="158">
-        <v>295029.98</v>
-      </c>
-      <c r="E36" s="124" t="s">
-        <v>231</v>
-      </c>
-      <c r="G36" s="133"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="100"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="158">
+        <v>295029.98</v>
+      </c>
+      <c r="E37" s="124" t="s">
+        <v>231</v>
+      </c>
+      <c r="G37" s="133"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="200">
+      <c r="C38" s="5"/>
+      <c r="D38" s="168">
         <v>26576.33</v>
       </c>
-      <c r="E37" s="109" t="s">
+      <c r="E38" s="109" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="str">
-        <f>A37</f>
-        <v>Sindicatos mes de MAYO</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="200">
-        <v>50388.03</v>
-      </c>
-      <c r="E38" s="109" t="str">
-        <f>E37</f>
-        <v>Debito 14/04</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2567,499 +2577,511 @@
         <v>Sindicatos mes de MAYO</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="168">
+        <v>50388.03</v>
+      </c>
+      <c r="E39" s="109" t="str">
+        <f>E38</f>
+        <v>Debito 14/04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="str">
+        <f>A39</f>
+        <v>Sindicatos mes de MAYO</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="200">
+      <c r="C40" s="5"/>
+      <c r="D40" s="168">
         <v>2952.93</v>
       </c>
-      <c r="E39" s="110" t="str">
-        <f>E37</f>
+      <c r="E40" s="110" t="str">
+        <f>E38</f>
         <v>Debito 14/04</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="26" t="s">
+    <row r="41" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="26" t="s">
         <v>3</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="99">
-        <f>SUM(D36:D39)</f>
-        <v>374947.26999999996</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="33" t="s">
-        <v>20</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="100"/>
-    </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="121">
-        <v>179199.38</v>
-      </c>
-      <c r="E42" s="107" t="s">
-        <v>229</v>
-      </c>
+      <c r="D41" s="39"/>
+      <c r="E41" s="99">
+        <f>SUM(D37:D40)</f>
+        <v>374947.26999999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="100"/>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>186</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="121">
         <v>179199.38</v>
       </c>
       <c r="E43" s="107" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B44" s="5"/>
+        <v>186</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="C44" s="5"/>
       <c r="D44" s="121">
-        <v>35000</v>
+        <v>179199.38</v>
       </c>
       <c r="E44" s="107" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="121">
-        <v>77164.73</v>
+        <v>35000</v>
       </c>
       <c r="E45" s="107" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="167" t="s">
+      <c r="A46" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B46" s="168"/>
+      <c r="B46" s="5"/>
       <c r="C46" s="5"/>
       <c r="D46" s="121">
+        <v>77164.73</v>
+      </c>
+      <c r="E46" s="107" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="172" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" s="173"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="121">
         <v>79061.399999999994</v>
       </c>
-      <c r="E46" s="107" t="s">
+      <c r="E47" s="107" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="26" t="s">
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="26" t="s">
         <v>4</v>
-      </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="99">
-        <f>SUM(D42:D46)</f>
-        <v>549624.89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="33" t="s">
-        <v>19</v>
       </c>
       <c r="B48" s="26"/>
       <c r="C48" s="26"/>
       <c r="D48" s="37"/>
-      <c r="E48" s="103"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="203" t="s">
+      <c r="E48" s="99">
+        <f>SUM(D43:D47)</f>
+        <v>549624.89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="103"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="180" t="s">
         <v>287</v>
       </c>
-      <c r="B49" s="204"/>
-      <c r="C49" s="65"/>
-      <c r="D49" s="200">
+      <c r="B50" s="181"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="168">
         <v>84500</v>
-      </c>
-      <c r="E49" s="102" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="203" t="s">
-        <v>287</v>
-      </c>
-      <c r="B50" s="204"/>
-      <c r="C50" s="65"/>
-      <c r="D50" s="200">
-        <v>262099.86</v>
       </c>
       <c r="E50" s="102" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="175" t="s">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="180" t="s">
+        <v>287</v>
+      </c>
+      <c r="B51" s="181"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="168">
+        <v>262099.86</v>
+      </c>
+      <c r="E51" s="102" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="182" t="s">
         <v>284</v>
       </c>
-      <c r="B51" s="176"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="200">
+      <c r="B52" s="183"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="168">
         <v>165000</v>
-      </c>
-      <c r="E51" s="102" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="167" t="s">
-        <v>283</v>
-      </c>
-      <c r="B52" s="168"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="200">
-        <v>230000</v>
       </c>
       <c r="E52" s="102" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="156" t="s">
-        <v>282</v>
+      <c r="A53" s="167" t="s">
+        <v>288</v>
       </c>
       <c r="B53" s="145"/>
       <c r="C53" s="55"/>
-      <c r="D53" s="200">
-        <v>385000</v>
+      <c r="D53" s="168">
+        <v>450000</v>
       </c>
       <c r="E53" s="102" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="156" t="s">
-        <v>280</v>
-      </c>
-      <c r="B54" s="145"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="172" t="s">
+        <v>283</v>
+      </c>
+      <c r="B54" s="173"/>
       <c r="C54" s="55"/>
-      <c r="D54" s="200">
-        <v>670000</v>
+      <c r="D54" s="168">
+        <v>230000</v>
       </c>
       <c r="E54" s="102" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="177" t="s">
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="156" t="s">
+        <v>282</v>
+      </c>
+      <c r="B55" s="145"/>
+      <c r="C55" s="55"/>
+      <c r="D55" s="168">
+        <v>385000</v>
+      </c>
+      <c r="E55" s="102" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="156" t="s">
+        <v>280</v>
+      </c>
+      <c r="B56" s="145"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="168">
+        <v>670000</v>
+      </c>
+      <c r="E56" s="102" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="184" t="s">
         <v>279</v>
       </c>
-      <c r="B55" s="178"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="121">
+      <c r="B57" s="185"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="121">
         <v>81500</v>
       </c>
-      <c r="E55" s="125" t="s">
+      <c r="E57" s="125" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="177" t="s">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="184" t="s">
         <v>226</v>
       </c>
-      <c r="B56" s="178"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="105">
+      <c r="B58" s="185"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="105">
         <v>202100</v>
       </c>
-      <c r="E56" s="102" t="s">
+      <c r="E58" s="102" t="s">
         <v>227</v>
       </c>
-      <c r="I56" s="167"/>
-      <c r="J56" s="168"/>
-    </row>
-    <row r="57" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="26" t="s">
+      <c r="I58" s="172"/>
+      <c r="J58" s="173"/>
+    </row>
+    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="201">
-        <f>SUM(D49:D56)</f>
-        <v>2080199.8599999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="33" t="s">
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="169">
+        <f>SUM(D50:D58)</f>
+        <v>2530199.86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B58" s="66"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="103"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
+      <c r="B60" s="66"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="103"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="121">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="121">
         <v>105869.88</v>
       </c>
-      <c r="E59" s="111"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
+      <c r="E61" s="111"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="121">
-        <v>49082</v>
-      </c>
-      <c r="E60" s="108"/>
-    </row>
-    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="B61" s="52"/>
-      <c r="C61" s="52"/>
-      <c r="D61" s="112"/>
-      <c r="E61" s="99">
-        <f>SUM(D59:D60)</f>
-        <v>154951.88</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="113"/>
+      <c r="D62" s="121">
+        <v>49082</v>
+      </c>
+      <c r="E62" s="108"/>
     </row>
     <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="112"/>
+      <c r="E63" s="99">
+        <f>SUM(D61:D62)</f>
+        <v>154951.88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="93"/>
+      <c r="E64" s="113"/>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="114"/>
-      <c r="E63" s="155">
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="114"/>
+      <c r="E65" s="155">
         <v>623172</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="1"/>
-      <c r="D64" s="115"/>
-      <c r="E64" s="116"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="162"/>
-    </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="D66" s="115"/>
+      <c r="E66" s="116"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="162"/>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="117"/>
-      <c r="E65" s="154">
-        <f>(SUM(E26:E63))</f>
-        <v>4963775.8</v>
-      </c>
-      <c r="F65" s="153"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D66" s="115"/>
-      <c r="E66" s="115"/>
-    </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D67" s="115"/>
-      <c r="E67" s="115"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
+      <c r="B67" s="10"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="117"/>
+      <c r="E67" s="154">
+        <f>(SUM(E26:E65))</f>
+        <v>5484643.7999999998</v>
+      </c>
+      <c r="F67" s="153"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D68" s="115"/>
+      <c r="E68" s="115"/>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D69" s="115"/>
+      <c r="E69" s="115"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="118"/>
-      <c r="E68" s="119"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="167" t="s">
+      <c r="B70" s="12"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="118"/>
+      <c r="E70" s="119"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="172" t="s">
         <v>285</v>
       </c>
-      <c r="B69" s="168"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="202">
+      <c r="B71" s="173"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="170">
         <v>568429.56999999995</v>
       </c>
-      <c r="E69" s="101" t="s">
+      <c r="E71" s="101" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="104"/>
-      <c r="B70" s="106"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="105"/>
-      <c r="E70" s="101"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="50"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57">
-        <f>SUM(D69:D70)</f>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="104"/>
+      <c r="B72" s="106"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="105"/>
+      <c r="E72" s="101"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="50"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57">
+        <f>SUM(D71:D72)</f>
         <v>568429.56999999995</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:6" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:6" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="179" t="s">
+    <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:7" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="186" t="s">
         <v>265</v>
       </c>
-      <c r="B74" s="180"/>
-      <c r="C74" s="180"/>
-      <c r="D74" s="181"/>
-      <c r="E74" s="163">
+      <c r="B76" s="187"/>
+      <c r="C76" s="187"/>
+      <c r="D76" s="188"/>
+      <c r="E76" s="163">
         <v>1000000</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
+    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="164">
-        <f>E71+E74</f>
+      <c r="B78" s="10"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="164">
+        <f>E73+E76</f>
         <v>1568429.5699999998</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="90" t="s">
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="B78" s="91">
-        <f>E65</f>
-        <v>4963775.8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="90" t="s">
-        <v>16</v>
-      </c>
-      <c r="B79" s="91">
-        <f>E65-E63</f>
-        <v>4340603.8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="90" t="s">
-        <v>25</v>
-      </c>
       <c r="B80" s="91">
-        <f>E76-E74</f>
-        <v>568429.56999999983</v>
+        <f>E67</f>
+        <v>5484643.7999999998</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="91">
+        <f>E67-E65</f>
+        <v>4861471.8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" s="91">
+        <f>E78-E76</f>
+        <v>568429.56999999983</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="B81" s="91">
-        <f>E76</f>
+      <c r="B83" s="91">
+        <f>E78</f>
         <v>1568429.5699999998</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="46" t="s">
+    <row r="84" spans="1:3" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B83" s="134"/>
-      <c r="C83" s="21"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="30" t="s">
+      <c r="B85" s="134"/>
+      <c r="C85" s="21"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="58">
+      <c r="B86" s="58">
         <v>131072.42461679748</v>
       </c>
-      <c r="C84" s="23"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="22" t="s">
+      <c r="C86" s="23"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="42">
+      <c r="B87" s="42">
         <f>PRORRATEO!H92</f>
         <v>6819818.0899999999</v>
       </c>
-      <c r="C85" s="21"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="22" t="s">
+      <c r="C87" s="21"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B86" s="108">
-        <f>B107</f>
+      <c r="B88" s="108">
+        <f>B109</f>
         <v>119259.82</v>
       </c>
-      <c r="C86" s="21"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="128" t="s">
+      <c r="C88" s="21"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="128" t="s">
         <v>46</v>
       </c>
-      <c r="B87" s="48">
+      <c r="B89" s="48">
         <f>-(846+54301)</f>
         <v>-55147</v>
-      </c>
-      <c r="C87" s="21"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="128" t="s">
-        <v>241</v>
-      </c>
-      <c r="B88" s="48">
-        <v>-163147</v>
-      </c>
-      <c r="C88" s="21"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="128" t="s">
-        <v>241</v>
-      </c>
-      <c r="B89" s="158">
-        <v>-113493</v>
       </c>
       <c r="C89" s="21"/>
     </row>
@@ -3067,8 +3089,8 @@
       <c r="A90" s="128" t="s">
         <v>241</v>
       </c>
-      <c r="B90" s="158">
-        <v>48097</v>
+      <c r="B90" s="48">
+        <v>-163147</v>
       </c>
       <c r="C90" s="21"/>
     </row>
@@ -3077,7 +3099,7 @@
         <v>241</v>
       </c>
       <c r="B91" s="158">
-        <v>-44900</v>
+        <v>-113493</v>
       </c>
       <c r="C91" s="21"/>
     </row>
@@ -3086,7 +3108,7 @@
         <v>241</v>
       </c>
       <c r="B92" s="158">
-        <v>-113493</v>
+        <v>48097</v>
       </c>
       <c r="C92" s="21"/>
     </row>
@@ -3095,7 +3117,7 @@
         <v>241</v>
       </c>
       <c r="B93" s="158">
-        <v>-141707</v>
+        <v>-44900</v>
       </c>
       <c r="C93" s="21"/>
     </row>
@@ -3103,175 +3125,193 @@
       <c r="A94" s="128" t="s">
         <v>241</v>
       </c>
-      <c r="B94" s="48">
+      <c r="B94" s="158">
+        <v>-113493</v>
+      </c>
+      <c r="C94" s="21"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="128" t="s">
+        <v>241</v>
+      </c>
+      <c r="B95" s="158">
+        <v>-141707</v>
+      </c>
+      <c r="C95" s="21"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="128" t="s">
+        <v>241</v>
+      </c>
+      <c r="B96" s="48">
         <v>20000</v>
       </c>
-      <c r="C94" s="21"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="41" t="s">
+      <c r="C96" s="21"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B95" s="48">
-        <f>-B79</f>
-        <v>-4340603.8</v>
-      </c>
-      <c r="C95" s="21"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="41" t="s">
+      <c r="B97" s="48">
+        <f>-B81</f>
+        <v>-4861471.8</v>
+      </c>
+      <c r="C97" s="21"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="B96" s="48">
+      <c r="B98" s="48">
         <f>-PRORRATEO!F1</f>
         <v>-2102777.02</v>
       </c>
-      <c r="C96" s="21"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A97" s="41" t="s">
+      <c r="C98" s="21"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="B97" s="48">
+      <c r="B99" s="48">
         <f>-PRORRATEO!F2</f>
         <v>-568429.56999999995</v>
       </c>
-      <c r="C97" s="21"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A98" s="25" t="s">
+      <c r="C99" s="21"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B98" s="48">
-        <f>-(B80)</f>
+      <c r="B100" s="48">
+        <f>-(B82)</f>
         <v>-568429.56999999983</v>
       </c>
-      <c r="C98" s="21"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="143" t="s">
+      <c r="C100" s="21"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="B99" s="144">
-        <f>SUM(B84:B98)</f>
-        <v>-1073879.6253832015</v>
-      </c>
-      <c r="C99" s="24"/>
-      <c r="D99" s="45"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B100" s="43"/>
-      <c r="C100" s="24"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="135"/>
-      <c r="F100" s="136"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B101" s="43"/>
+      <c r="B101" s="144">
+        <f>SUM(B86:B100)</f>
+        <v>-1594747.6253832015</v>
+      </c>
       <c r="C101" s="24"/>
       <c r="D101" s="45"/>
-      <c r="E101" s="135"/>
-      <c r="F101" s="136"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="174" t="s">
+      <c r="B102" s="43"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="45"/>
+      <c r="E102" s="135"/>
+      <c r="F102" s="136"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B103" s="43"/>
+      <c r="C103" s="24"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="135"/>
+      <c r="F103" s="136"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A104" s="179" t="s">
         <v>35</v>
       </c>
-      <c r="B102" s="174"/>
-      <c r="C102" s="174"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="174"/>
-      <c r="B103" s="174"/>
-      <c r="C103" s="174"/>
-    </row>
-    <row r="104" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="54" t="s">
+      <c r="B104" s="179"/>
+      <c r="C104" s="179"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="179"/>
+      <c r="B105" s="179"/>
+      <c r="C105" s="179"/>
+    </row>
+    <row r="106" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="B104" s="36">
+      <c r="B106" s="36">
         <v>28214</v>
       </c>
-      <c r="C104" s="36">
+      <c r="C106" s="36">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="54" t="s">
+    <row r="107" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="B105" s="36">
+      <c r="B107" s="36">
         <v>1065</v>
       </c>
-      <c r="C105" s="36"/>
-    </row>
-    <row r="106" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="147" t="s">
+      <c r="C107" s="36"/>
+    </row>
+    <row r="108" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="147" t="s">
         <v>260</v>
       </c>
-      <c r="B106" s="36">
+      <c r="B108" s="36">
         <v>89980.82</v>
       </c>
-      <c r="C106" s="36">
+      <c r="C108" s="36">
         <v>61209</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="46" t="s">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B107" s="120">
-        <f>SUM(B104:B106)</f>
+      <c r="B109" s="120">
+        <f>SUM(B106:B108)</f>
         <v>119259.82</v>
       </c>
-      <c r="C107" s="47"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M108" s="8"/>
-    </row>
-    <row r="109" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="173"/>
-      <c r="B109" s="173"/>
-      <c r="C109" s="173"/>
-      <c r="D109" s="173"/>
-      <c r="E109" s="173"/>
+      <c r="C109" s="47"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A110" s="173"/>
-      <c r="B110" s="173"/>
-      <c r="C110" s="173"/>
-      <c r="D110" s="173"/>
-      <c r="E110" s="173"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A111" s="173"/>
-      <c r="B111" s="173"/>
-      <c r="C111" s="173"/>
-      <c r="D111" s="173"/>
-      <c r="E111" s="173"/>
+      <c r="M110" s="8"/>
+    </row>
+    <row r="111" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="178"/>
+      <c r="B111" s="178"/>
+      <c r="C111" s="178"/>
+      <c r="D111" s="178"/>
+      <c r="E111" s="178"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A112" s="173"/>
-      <c r="B112" s="173"/>
-      <c r="C112" s="173"/>
-      <c r="D112" s="173"/>
-      <c r="E112" s="173"/>
+      <c r="A112" s="178"/>
+      <c r="B112" s="178"/>
+      <c r="C112" s="178"/>
+      <c r="D112" s="178"/>
+      <c r="E112" s="178"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="178"/>
+      <c r="B113" s="178"/>
+      <c r="C113" s="178"/>
+      <c r="D113" s="178"/>
+      <c r="E113" s="178"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="178"/>
+      <c r="B114" s="178"/>
+      <c r="C114" s="178"/>
+      <c r="D114" s="178"/>
+      <c r="E114" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="A109:E112"/>
-    <mergeCell ref="A102:C103"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="A111:E114"/>
+    <mergeCell ref="A104:C105"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="B5:E5"/>
@@ -3318,10 +3358,10 @@
       <c r="E1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="191">
+      <c r="F1" s="198">
         <v>2102777.02</v>
       </c>
-      <c r="G1" s="191"/>
+      <c r="G1" s="198"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3329,16 +3369,16 @@
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="193">
+      <c r="M1" s="200">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="193"/>
+      <c r="N1" s="200"/>
       <c r="O1" s="157"/>
-      <c r="P1" s="198">
+      <c r="P1" s="205">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="198"/>
+      <c r="Q1" s="205"/>
       <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3351,103 +3391,103 @@
       <c r="E2" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="192">
+      <c r="F2" s="199">
         <v>568429.56999999995</v>
       </c>
-      <c r="G2" s="192"/>
+      <c r="G2" s="199"/>
       <c r="H2" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="I2" s="197">
+      <c r="I2" s="204">
         <v>1000000</v>
       </c>
-      <c r="J2" s="197"/>
+      <c r="J2" s="204"/>
       <c r="K2" s="6" t="s">
         <v>264</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="197">
+      <c r="M2" s="204">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="197"/>
+      <c r="N2" s="204"/>
       <c r="O2" s="159"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="199"/>
+      <c r="P2" s="206"/>
+      <c r="Q2" s="206"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="189" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="129"/>
-      <c r="C3" s="184" t="s">
+      <c r="C3" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="184" t="s">
+      <c r="D3" s="191" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="184" t="s">
+      <c r="E3" s="191" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="184" t="s">
+      <c r="F3" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="186" t="s">
+      <c r="G3" s="193" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="184" t="s">
+      <c r="H3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="188" t="s">
+      <c r="I3" s="195" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="186" t="s">
+      <c r="J3" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="186" t="str">
+      <c r="K3" s="193" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="186" t="s">
+      <c r="L3" s="193" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="186" t="s">
+      <c r="M3" s="193" t="s">
         <v>182</v>
       </c>
-      <c r="N3" s="186" t="s">
+      <c r="N3" s="193" t="s">
         <v>183</v>
       </c>
-      <c r="O3" s="186" t="s">
+      <c r="O3" s="193" t="s">
         <v>266</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="194" t="s">
+      <c r="Q3" s="201" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="45"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="183"/>
+      <c r="A4" s="190"/>
       <c r="B4" s="130"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="187"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="187"/>
-      <c r="O4" s="187"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="194"/>
+      <c r="K4" s="197"/>
+      <c r="L4" s="194"/>
+      <c r="M4" s="194"/>
+      <c r="N4" s="194"/>
+      <c r="O4" s="194"/>
       <c r="P4" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q4" s="195"/>
+      <c r="Q4" s="202"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="62"/>
@@ -9067,97 +9107,97 @@
       <c r="E93" s="51"/>
     </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="173" t="str">
+      <c r="D95" s="178" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="173"/>
-      <c r="F95" s="173"/>
-      <c r="G95" s="173"/>
-      <c r="H95" s="173"/>
-      <c r="I95" s="173"/>
-      <c r="J95" s="173"/>
-      <c r="K95" s="173"/>
-      <c r="L95" s="173"/>
-      <c r="M95" s="173"/>
-      <c r="N95" s="173"/>
-      <c r="O95" s="173"/>
-      <c r="P95" s="173"/>
+      <c r="E95" s="178"/>
+      <c r="F95" s="178"/>
+      <c r="G95" s="178"/>
+      <c r="H95" s="178"/>
+      <c r="I95" s="178"/>
+      <c r="J95" s="178"/>
+      <c r="K95" s="178"/>
+      <c r="L95" s="178"/>
+      <c r="M95" s="178"/>
+      <c r="N95" s="178"/>
+      <c r="O95" s="178"/>
+      <c r="P95" s="178"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="173"/>
-      <c r="E96" s="173"/>
-      <c r="F96" s="173"/>
-      <c r="G96" s="173"/>
-      <c r="H96" s="173"/>
-      <c r="I96" s="173"/>
-      <c r="J96" s="173"/>
-      <c r="K96" s="173"/>
-      <c r="L96" s="173"/>
-      <c r="M96" s="173"/>
-      <c r="N96" s="173"/>
-      <c r="O96" s="173"/>
-      <c r="P96" s="173"/>
+      <c r="D96" s="178"/>
+      <c r="E96" s="178"/>
+      <c r="F96" s="178"/>
+      <c r="G96" s="178"/>
+      <c r="H96" s="178"/>
+      <c r="I96" s="178"/>
+      <c r="J96" s="178"/>
+      <c r="K96" s="178"/>
+      <c r="L96" s="178"/>
+      <c r="M96" s="178"/>
+      <c r="N96" s="178"/>
+      <c r="O96" s="178"/>
+      <c r="P96" s="178"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="173"/>
-      <c r="E97" s="173"/>
-      <c r="F97" s="173"/>
-      <c r="G97" s="173"/>
-      <c r="H97" s="173"/>
-      <c r="I97" s="173"/>
-      <c r="J97" s="173"/>
-      <c r="K97" s="173"/>
-      <c r="L97" s="173"/>
-      <c r="M97" s="173"/>
-      <c r="N97" s="173"/>
-      <c r="O97" s="173"/>
-      <c r="P97" s="173"/>
+      <c r="D97" s="178"/>
+      <c r="E97" s="178"/>
+      <c r="F97" s="178"/>
+      <c r="G97" s="178"/>
+      <c r="H97" s="178"/>
+      <c r="I97" s="178"/>
+      <c r="J97" s="178"/>
+      <c r="K97" s="178"/>
+      <c r="L97" s="178"/>
+      <c r="M97" s="178"/>
+      <c r="N97" s="178"/>
+      <c r="O97" s="178"/>
+      <c r="P97" s="178"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="173"/>
-      <c r="E98" s="173"/>
-      <c r="F98" s="173"/>
-      <c r="G98" s="173"/>
-      <c r="H98" s="173"/>
-      <c r="I98" s="173"/>
-      <c r="J98" s="173"/>
-      <c r="K98" s="173"/>
-      <c r="L98" s="173"/>
-      <c r="M98" s="173"/>
-      <c r="N98" s="173"/>
-      <c r="O98" s="173"/>
-      <c r="P98" s="173"/>
+      <c r="D98" s="178"/>
+      <c r="E98" s="178"/>
+      <c r="F98" s="178"/>
+      <c r="G98" s="178"/>
+      <c r="H98" s="178"/>
+      <c r="I98" s="178"/>
+      <c r="J98" s="178"/>
+      <c r="K98" s="178"/>
+      <c r="L98" s="178"/>
+      <c r="M98" s="178"/>
+      <c r="N98" s="178"/>
+      <c r="O98" s="178"/>
+      <c r="P98" s="178"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="173"/>
-      <c r="E99" s="173"/>
-      <c r="F99" s="173"/>
-      <c r="G99" s="173"/>
-      <c r="H99" s="173"/>
-      <c r="I99" s="173"/>
-      <c r="J99" s="173"/>
-      <c r="K99" s="173"/>
-      <c r="L99" s="173"/>
-      <c r="M99" s="173"/>
-      <c r="N99" s="173"/>
-      <c r="O99" s="173"/>
-      <c r="P99" s="173"/>
+      <c r="D99" s="178"/>
+      <c r="E99" s="178"/>
+      <c r="F99" s="178"/>
+      <c r="G99" s="178"/>
+      <c r="H99" s="178"/>
+      <c r="I99" s="178"/>
+      <c r="J99" s="178"/>
+      <c r="K99" s="178"/>
+      <c r="L99" s="178"/>
+      <c r="M99" s="178"/>
+      <c r="N99" s="178"/>
+      <c r="O99" s="178"/>
+      <c r="P99" s="178"/>
     </row>
     <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="173"/>
-      <c r="E100" s="173"/>
-      <c r="F100" s="173"/>
-      <c r="G100" s="173"/>
-      <c r="H100" s="173"/>
-      <c r="I100" s="173"/>
-      <c r="J100" s="173"/>
-      <c r="K100" s="173"/>
-      <c r="L100" s="173"/>
-      <c r="M100" s="173"/>
-      <c r="N100" s="173"/>
-      <c r="O100" s="173"/>
-      <c r="P100" s="173"/>
+      <c r="D100" s="178"/>
+      <c r="E100" s="178"/>
+      <c r="F100" s="178"/>
+      <c r="G100" s="178"/>
+      <c r="H100" s="178"/>
+      <c r="I100" s="178"/>
+      <c r="J100" s="178"/>
+      <c r="K100" s="178"/>
+      <c r="L100" s="178"/>
+      <c r="M100" s="178"/>
+      <c r="N100" s="178"/>
+      <c r="O100" s="178"/>
+      <c r="P100" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/VERGARA/Mayo/vergara MAYO.xlsx
+++ b/VERGARA/Mayo/vergara MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73534D49-ACAF-4E70-B8CD-FEB8EAFE16F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79516097-E447-42D2-A097-56AD91D83CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,12 +705,6 @@
     <t>Magali Carrivale</t>
   </si>
   <si>
-    <t>Romanatti Carlos cioua de reglamento digital de copropiedad</t>
-  </si>
-  <si>
-    <t>Tranfs 10/04</t>
-  </si>
-  <si>
     <t>Vto 01/04</t>
   </si>
   <si>
@@ -897,6 +891,12 @@
   </si>
   <si>
     <t>Transf 21/05</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Deteccion de cortocircuito y ajuste de todas las termicas</t>
+  </si>
+  <si>
+    <t>Transf 26/05</t>
   </si>
 </sst>
 </file>
@@ -1752,23 +1752,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1803,32 +1797,17 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1845,8 +1824,17 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1857,11 +1845,23 @@
     <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2287,12 +2287,12 @@
       <c r="A5" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="174" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="175"/>
+      <c r="B5" s="187" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="187"/>
+      <c r="D5" s="187"/>
+      <c r="E5" s="188"/>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
@@ -2306,49 +2306,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="177" t="s">
-        <v>274</v>
-      </c>
-      <c r="C8" s="177"/>
+      <c r="B8" s="190" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="190"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="177"/>
-      <c r="C9" s="177"/>
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="177"/>
-      <c r="C10" s="177"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="176" t="s">
+      <c r="A13" s="189" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
+      <c r="B13" s="189"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="176"/>
-      <c r="B14" s="176"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
+      <c r="A14" s="189"/>
+      <c r="B14" s="189"/>
+      <c r="C14" s="189"/>
+      <c r="D14" s="189"/>
+      <c r="E14" s="189"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="176"/>
-      <c r="B15" s="176"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="176"/>
+      <c r="A15" s="189"/>
+      <c r="B15" s="189"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="176"/>
-      <c r="B16" s="176"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="176"/>
+      <c r="A16" s="189"/>
+      <c r="B16" s="189"/>
+      <c r="C16" s="189"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2444,29 +2444,29 @@
       <c r="E27" s="96"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="172" t="s">
-        <v>276</v>
-      </c>
-      <c r="B28" s="173"/>
+      <c r="A28" s="174" t="s">
+        <v>274</v>
+      </c>
+      <c r="B28" s="175"/>
       <c r="C28" s="5"/>
       <c r="D28" s="126">
         <v>31000</v>
       </c>
       <c r="E28" s="97" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="172" t="s">
-        <v>278</v>
-      </c>
-      <c r="B29" s="173"/>
+      <c r="A29" s="174" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" s="175"/>
       <c r="C29" s="5"/>
       <c r="D29" s="126">
         <v>470000</v>
       </c>
       <c r="E29" s="97" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2491,10 +2491,10 @@
       <c r="E31" s="67"/>
     </row>
     <row r="32" spans="1:7" s="40" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="172" t="s">
+      <c r="A32" s="174" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="173"/>
+      <c r="B32" s="175"/>
       <c r="C32" s="54"/>
       <c r="D32" s="138">
         <v>226692</v>
@@ -2502,19 +2502,19 @@
       <c r="E32" s="122"/>
     </row>
     <row r="33" spans="1:7" s="40" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="208"/>
+      <c r="A33" s="173"/>
       <c r="B33" s="171"/>
       <c r="C33" s="54"/>
-      <c r="D33" s="207">
+      <c r="D33" s="172">
         <v>70868</v>
       </c>
       <c r="E33" s="122"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="172" t="s">
+      <c r="A34" s="174" t="s">
         <v>220</v>
       </c>
-      <c r="B34" s="173"/>
+      <c r="B34" s="175"/>
       <c r="C34" s="54"/>
       <c r="D34" s="127">
         <v>719.9</v>
@@ -2552,13 +2552,13 @@
         <v>295029.98</v>
       </c>
       <c r="E37" s="124" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G37" s="133"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>22</v>
@@ -2568,7 +2568,7 @@
         <v>26576.33</v>
       </c>
       <c r="E38" s="109" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2631,14 +2631,14 @@
         <v>186</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="121">
         <v>179199.38</v>
       </c>
       <c r="E43" s="107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2646,14 +2646,14 @@
         <v>186</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="121">
         <v>179199.38</v>
       </c>
       <c r="E44" s="107" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2666,12 +2666,12 @@
         <v>35000</v>
       </c>
       <c r="E45" s="107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2679,20 +2679,20 @@
         <v>77164.73</v>
       </c>
       <c r="E46" s="107" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="172" t="s">
-        <v>237</v>
-      </c>
-      <c r="B47" s="173"/>
+      <c r="A47" s="174" t="s">
+        <v>235</v>
+      </c>
+      <c r="B47" s="175"/>
       <c r="C47" s="5"/>
       <c r="D47" s="121">
         <v>79061.399999999994</v>
       </c>
       <c r="E47" s="107" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2717,47 +2717,47 @@
       <c r="E49" s="103"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="180" t="s">
-        <v>287</v>
-      </c>
-      <c r="B50" s="181"/>
+      <c r="A50" s="178" t="s">
+        <v>285</v>
+      </c>
+      <c r="B50" s="179"/>
       <c r="C50" s="65"/>
       <c r="D50" s="168">
         <v>84500</v>
       </c>
       <c r="E50" s="102" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="180" t="s">
-        <v>287</v>
-      </c>
-      <c r="B51" s="181"/>
+      <c r="A51" s="178" t="s">
+        <v>285</v>
+      </c>
+      <c r="B51" s="179"/>
       <c r="C51" s="65"/>
       <c r="D51" s="168">
         <v>262099.86</v>
       </c>
       <c r="E51" s="102" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="182" t="s">
-        <v>284</v>
-      </c>
-      <c r="B52" s="183"/>
+      <c r="A52" s="180" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="181"/>
       <c r="C52" s="55"/>
       <c r="D52" s="168">
         <v>165000</v>
       </c>
       <c r="E52" s="102" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="167" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B53" s="145"/>
       <c r="C53" s="55"/>
@@ -2765,25 +2765,25 @@
         <v>450000</v>
       </c>
       <c r="E53" s="102" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="172" t="s">
-        <v>283</v>
-      </c>
-      <c r="B54" s="173"/>
+      <c r="A54" s="174" t="s">
+        <v>281</v>
+      </c>
+      <c r="B54" s="175"/>
       <c r="C54" s="55"/>
       <c r="D54" s="168">
         <v>230000</v>
       </c>
       <c r="E54" s="102" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="156" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B55" s="145"/>
       <c r="C55" s="55"/>
@@ -2791,12 +2791,12 @@
         <v>385000</v>
       </c>
       <c r="E55" s="102" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="156" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B56" s="145"/>
       <c r="C56" s="55"/>
@@ -2804,36 +2804,36 @@
         <v>670000</v>
       </c>
       <c r="E56" s="102" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="184" t="s">
-        <v>279</v>
-      </c>
-      <c r="B57" s="185"/>
+      <c r="A57" s="182" t="s">
+        <v>277</v>
+      </c>
+      <c r="B57" s="183"/>
       <c r="C57" s="5"/>
       <c r="D57" s="121">
         <v>81500</v>
       </c>
       <c r="E57" s="125" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="184" t="s">
-        <v>226</v>
-      </c>
-      <c r="B58" s="185"/>
+      <c r="A58" s="182" t="s">
+        <v>288</v>
+      </c>
+      <c r="B58" s="183"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="105">
-        <v>202100</v>
+      <c r="D58" s="170">
+        <v>150000</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>227</v>
-      </c>
-      <c r="I58" s="172"/>
-      <c r="J58" s="173"/>
+        <v>289</v>
+      </c>
+      <c r="I58" s="174"/>
+      <c r="J58" s="175"/>
     </row>
     <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="26" t="s">
@@ -2844,7 +2844,7 @@
       <c r="D59" s="31"/>
       <c r="E59" s="169">
         <f>SUM(D50:D58)</f>
-        <v>2530199.86</v>
+        <v>2478099.86</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2899,7 +2899,7 @@
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B65" s="29"/>
       <c r="C65" s="29"/>
@@ -2924,7 +2924,7 @@
       <c r="D67" s="117"/>
       <c r="E67" s="154">
         <f>(SUM(E26:E65))</f>
-        <v>5484643.7999999998</v>
+        <v>5432543.7999999998</v>
       </c>
       <c r="F67" s="153"/>
     </row>
@@ -2946,16 +2946,16 @@
       <c r="E70" s="119"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="172" t="s">
-        <v>285</v>
-      </c>
-      <c r="B71" s="173"/>
+      <c r="A71" s="174" t="s">
+        <v>283</v>
+      </c>
+      <c r="B71" s="175"/>
       <c r="C71" s="5"/>
       <c r="D71" s="170">
         <v>568429.56999999995</v>
       </c>
       <c r="E71" s="101" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2978,12 +2978,12 @@
     <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="76" spans="1:7" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="186" t="s">
-        <v>265</v>
-      </c>
-      <c r="B76" s="187"/>
-      <c r="C76" s="187"/>
-      <c r="D76" s="188"/>
+      <c r="A76" s="184" t="s">
+        <v>263</v>
+      </c>
+      <c r="B76" s="185"/>
+      <c r="C76" s="185"/>
+      <c r="D76" s="186"/>
       <c r="E76" s="163">
         <v>1000000</v>
       </c>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B80" s="91">
         <f>E67</f>
-        <v>5484643.7999999998</v>
+        <v>5432543.7999999998</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B81" s="91">
         <f>E67-E65</f>
-        <v>4861471.8</v>
+        <v>4809371.8</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3087,7 +3087,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B90" s="48">
         <v>-163147</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B91" s="158">
         <v>-113493</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B92" s="158">
         <v>48097</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B93" s="158">
         <v>-44900</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B94" s="158">
         <v>-113493</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B95" s="158">
         <v>-141707</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B96" s="48">
         <v>20000</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B97" s="48">
         <f>-B81</f>
-        <v>-4861471.8</v>
+        <v>-4809371.8</v>
       </c>
       <c r="C97" s="21"/>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B101" s="144">
         <f>SUM(B86:B100)</f>
-        <v>-1594747.6253832015</v>
+        <v>-1542647.6253832015</v>
       </c>
       <c r="C101" s="24"/>
       <c r="D101" s="45"/>
@@ -3214,20 +3214,20 @@
       <c r="F103" s="136"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="179" t="s">
+      <c r="A104" s="177" t="s">
         <v>35</v>
       </c>
-      <c r="B104" s="179"/>
-      <c r="C104" s="179"/>
+      <c r="B104" s="177"/>
+      <c r="C104" s="177"/>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="179"/>
-      <c r="B105" s="179"/>
-      <c r="C105" s="179"/>
+      <c r="A105" s="177"/>
+      <c r="B105" s="177"/>
+      <c r="C105" s="177"/>
     </row>
     <row r="106" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B106" s="36">
         <v>28214</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="107" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="54" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B107" s="36">
         <v>1065</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="108" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="147" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B108" s="36">
         <v>89980.82</v>
@@ -3270,35 +3270,43 @@
       <c r="M110" s="8"/>
     </row>
     <row r="111" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="178"/>
-      <c r="B111" s="178"/>
-      <c r="C111" s="178"/>
-      <c r="D111" s="178"/>
-      <c r="E111" s="178"/>
+      <c r="A111" s="176"/>
+      <c r="B111" s="176"/>
+      <c r="C111" s="176"/>
+      <c r="D111" s="176"/>
+      <c r="E111" s="176"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A112" s="178"/>
-      <c r="B112" s="178"/>
-      <c r="C112" s="178"/>
-      <c r="D112" s="178"/>
-      <c r="E112" s="178"/>
+      <c r="A112" s="176"/>
+      <c r="B112" s="176"/>
+      <c r="C112" s="176"/>
+      <c r="D112" s="176"/>
+      <c r="E112" s="176"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="178"/>
-      <c r="B113" s="178"/>
-      <c r="C113" s="178"/>
-      <c r="D113" s="178"/>
-      <c r="E113" s="178"/>
+      <c r="A113" s="176"/>
+      <c r="B113" s="176"/>
+      <c r="C113" s="176"/>
+      <c r="D113" s="176"/>
+      <c r="E113" s="176"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="178"/>
-      <c r="B114" s="178"/>
-      <c r="C114" s="178"/>
-      <c r="D114" s="178"/>
-      <c r="E114" s="178"/>
+      <c r="A114" s="176"/>
+      <c r="B114" s="176"/>
+      <c r="C114" s="176"/>
+      <c r="D114" s="176"/>
+      <c r="E114" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="A111:E114"/>
     <mergeCell ref="A104:C105"/>
@@ -3310,14 +3318,6 @@
     <mergeCell ref="A76:D76"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3353,15 +3353,15 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="198">
+      <c r="F1" s="191">
         <v>2102777.02</v>
       </c>
-      <c r="G1" s="198"/>
+      <c r="G1" s="191"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3369,16 +3369,16 @@
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="200">
+      <c r="M1" s="193">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="200"/>
+      <c r="N1" s="193"/>
       <c r="O1" s="157"/>
-      <c r="P1" s="205">
+      <c r="P1" s="201">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="205"/>
+      <c r="Q1" s="201"/>
       <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3386,108 +3386,108 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="199">
+      <c r="F2" s="192">
         <v>568429.56999999995</v>
       </c>
-      <c r="G2" s="199"/>
+      <c r="G2" s="192"/>
       <c r="H2" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="I2" s="204">
+        <v>265</v>
+      </c>
+      <c r="I2" s="200">
         <v>1000000</v>
       </c>
-      <c r="J2" s="204"/>
+      <c r="J2" s="200"/>
       <c r="K2" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="204">
+      <c r="M2" s="200">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="200"/>
       <c r="O2" s="159"/>
-      <c r="P2" s="206"/>
-      <c r="Q2" s="206"/>
+      <c r="P2" s="202"/>
+      <c r="Q2" s="202"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="203" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="129"/>
-      <c r="C3" s="191" t="s">
+      <c r="C3" s="196" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="191" t="s">
+      <c r="D3" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="191" t="s">
+      <c r="E3" s="196" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="191" t="s">
+      <c r="F3" s="196" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="193" t="s">
+      <c r="G3" s="198" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="191" t="s">
+      <c r="H3" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="193" t="s">
+      <c r="J3" s="198" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="193" t="str">
+      <c r="K3" s="198" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="193" t="s">
+      <c r="L3" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="193" t="s">
+      <c r="M3" s="198" t="s">
         <v>182</v>
       </c>
-      <c r="N3" s="193" t="s">
+      <c r="N3" s="198" t="s">
         <v>183</v>
       </c>
-      <c r="O3" s="193" t="s">
-        <v>266</v>
+      <c r="O3" s="198" t="s">
+        <v>264</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="201" t="s">
+      <c r="Q3" s="194" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="45"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="190"/>
+      <c r="A4" s="204"/>
       <c r="B4" s="130"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="194"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="194"/>
-      <c r="K4" s="197"/>
-      <c r="L4" s="194"/>
-      <c r="M4" s="194"/>
-      <c r="N4" s="194"/>
-      <c r="O4" s="194"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="199"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="199"/>
+      <c r="M4" s="199"/>
+      <c r="N4" s="199"/>
+      <c r="O4" s="199"/>
       <c r="P4" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q4" s="202"/>
+      <c r="Q4" s="195"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="62"/>
@@ -3758,7 +3758,7 @@
         <v>57</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F9" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4023,7 +4023,7 @@
         <v>64</v>
       </c>
       <c r="E13" s="63" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F13" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4421,7 +4421,7 @@
         <v>66</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F19" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4471,7 +4471,7 @@
         <v>0.47</v>
       </c>
       <c r="S19" s="49" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -4488,7 +4488,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="62" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F20" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4541,7 +4541,7 @@
         <v>0.48</v>
       </c>
       <c r="S20" s="49" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="T20" s="44"/>
     </row>
@@ -4559,7 +4559,7 @@
         <v>66</v>
       </c>
       <c r="E21" s="63" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F21" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4688,7 +4688,7 @@
         <v>66</v>
       </c>
       <c r="E23" s="63" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F23" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4953,7 +4953,7 @@
         <v>84</v>
       </c>
       <c r="E27" s="63" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F27" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5020,7 +5020,7 @@
         <v>86</v>
       </c>
       <c r="E28" s="63" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F28" s="71">
         <v>2.0199999999999999E-2</v>
@@ -5152,7 +5152,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="62" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F30" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5546,7 +5546,7 @@
         <v>102</v>
       </c>
       <c r="E36" s="63" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F36" s="71">
         <v>2.0199999999999999E-2</v>
@@ -6076,7 +6076,7 @@
         <v>115</v>
       </c>
       <c r="E44" s="61" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F44" s="80">
         <v>2.0199999999999999E-2</v>
@@ -6143,7 +6143,7 @@
         <v>118</v>
       </c>
       <c r="E45" s="61" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F45" s="80">
         <v>2.0199999999999999E-2</v>
@@ -6277,7 +6277,7 @@
         <v>122</v>
       </c>
       <c r="E47" s="79" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F47" s="80">
         <v>1.3899999999999999E-2</v>
@@ -6329,7 +6329,7 @@
         <v>0.75</v>
       </c>
       <c r="T47" s="165" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -6413,7 +6413,7 @@
         <v>115</v>
       </c>
       <c r="E49" s="61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F49" s="80">
         <v>2.0199999999999999E-2</v>
@@ -6479,7 +6479,7 @@
         <v>115</v>
       </c>
       <c r="E50" s="61" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F50" s="80">
         <v>1.3899999999999999E-2</v>
@@ -6611,7 +6611,7 @@
         <v>130</v>
       </c>
       <c r="E52" s="61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F52" s="80">
         <v>2.0199999999999999E-2</v>
@@ -6678,7 +6678,7 @@
         <v>132</v>
       </c>
       <c r="E53" s="61" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F53" s="80">
         <v>2.0199999999999999E-2</v>
@@ -6741,7 +6741,7 @@
         <v>82</v>
       </c>
       <c r="D54" s="161" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E54" s="161"/>
       <c r="F54" s="80">
@@ -6806,7 +6806,7 @@
         <v>135</v>
       </c>
       <c r="E55" s="61" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F55" s="80">
         <v>1.3899999999999999E-2</v>
@@ -7269,7 +7269,7 @@
         <v>145</v>
       </c>
       <c r="E63" s="63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F63" s="80">
         <v>2.0000000000000001E-4</v>
@@ -7401,7 +7401,7 @@
         <v>86</v>
       </c>
       <c r="E65" s="63" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F65" s="80">
         <v>2.0000000000000001E-4</v>
@@ -8848,7 +8848,7 @@
         <v>86</v>
       </c>
       <c r="E88" s="63" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F88" s="71">
         <v>5.3E-3</v>
@@ -9107,100 +9107,111 @@
       <c r="E93" s="51"/>
     </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="178" t="str">
+      <c r="D95" s="176" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="178"/>
-      <c r="F95" s="178"/>
-      <c r="G95" s="178"/>
-      <c r="H95" s="178"/>
-      <c r="I95" s="178"/>
-      <c r="J95" s="178"/>
-      <c r="K95" s="178"/>
-      <c r="L95" s="178"/>
-      <c r="M95" s="178"/>
-      <c r="N95" s="178"/>
-      <c r="O95" s="178"/>
-      <c r="P95" s="178"/>
+      <c r="E95" s="176"/>
+      <c r="F95" s="176"/>
+      <c r="G95" s="176"/>
+      <c r="H95" s="176"/>
+      <c r="I95" s="176"/>
+      <c r="J95" s="176"/>
+      <c r="K95" s="176"/>
+      <c r="L95" s="176"/>
+      <c r="M95" s="176"/>
+      <c r="N95" s="176"/>
+      <c r="O95" s="176"/>
+      <c r="P95" s="176"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="178"/>
-      <c r="E96" s="178"/>
-      <c r="F96" s="178"/>
-      <c r="G96" s="178"/>
-      <c r="H96" s="178"/>
-      <c r="I96" s="178"/>
-      <c r="J96" s="178"/>
-      <c r="K96" s="178"/>
-      <c r="L96" s="178"/>
-      <c r="M96" s="178"/>
-      <c r="N96" s="178"/>
-      <c r="O96" s="178"/>
-      <c r="P96" s="178"/>
+      <c r="D96" s="176"/>
+      <c r="E96" s="176"/>
+      <c r="F96" s="176"/>
+      <c r="G96" s="176"/>
+      <c r="H96" s="176"/>
+      <c r="I96" s="176"/>
+      <c r="J96" s="176"/>
+      <c r="K96" s="176"/>
+      <c r="L96" s="176"/>
+      <c r="M96" s="176"/>
+      <c r="N96" s="176"/>
+      <c r="O96" s="176"/>
+      <c r="P96" s="176"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="178"/>
-      <c r="E97" s="178"/>
-      <c r="F97" s="178"/>
-      <c r="G97" s="178"/>
-      <c r="H97" s="178"/>
-      <c r="I97" s="178"/>
-      <c r="J97" s="178"/>
-      <c r="K97" s="178"/>
-      <c r="L97" s="178"/>
-      <c r="M97" s="178"/>
-      <c r="N97" s="178"/>
-      <c r="O97" s="178"/>
-      <c r="P97" s="178"/>
+      <c r="D97" s="176"/>
+      <c r="E97" s="176"/>
+      <c r="F97" s="176"/>
+      <c r="G97" s="176"/>
+      <c r="H97" s="176"/>
+      <c r="I97" s="176"/>
+      <c r="J97" s="176"/>
+      <c r="K97" s="176"/>
+      <c r="L97" s="176"/>
+      <c r="M97" s="176"/>
+      <c r="N97" s="176"/>
+      <c r="O97" s="176"/>
+      <c r="P97" s="176"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="178"/>
-      <c r="E98" s="178"/>
-      <c r="F98" s="178"/>
-      <c r="G98" s="178"/>
-      <c r="H98" s="178"/>
-      <c r="I98" s="178"/>
-      <c r="J98" s="178"/>
-      <c r="K98" s="178"/>
-      <c r="L98" s="178"/>
-      <c r="M98" s="178"/>
-      <c r="N98" s="178"/>
-      <c r="O98" s="178"/>
-      <c r="P98" s="178"/>
+      <c r="D98" s="176"/>
+      <c r="E98" s="176"/>
+      <c r="F98" s="176"/>
+      <c r="G98" s="176"/>
+      <c r="H98" s="176"/>
+      <c r="I98" s="176"/>
+      <c r="J98" s="176"/>
+      <c r="K98" s="176"/>
+      <c r="L98" s="176"/>
+      <c r="M98" s="176"/>
+      <c r="N98" s="176"/>
+      <c r="O98" s="176"/>
+      <c r="P98" s="176"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="178"/>
-      <c r="E99" s="178"/>
-      <c r="F99" s="178"/>
-      <c r="G99" s="178"/>
-      <c r="H99" s="178"/>
-      <c r="I99" s="178"/>
-      <c r="J99" s="178"/>
-      <c r="K99" s="178"/>
-      <c r="L99" s="178"/>
-      <c r="M99" s="178"/>
-      <c r="N99" s="178"/>
-      <c r="O99" s="178"/>
-      <c r="P99" s="178"/>
+      <c r="D99" s="176"/>
+      <c r="E99" s="176"/>
+      <c r="F99" s="176"/>
+      <c r="G99" s="176"/>
+      <c r="H99" s="176"/>
+      <c r="I99" s="176"/>
+      <c r="J99" s="176"/>
+      <c r="K99" s="176"/>
+      <c r="L99" s="176"/>
+      <c r="M99" s="176"/>
+      <c r="N99" s="176"/>
+      <c r="O99" s="176"/>
+      <c r="P99" s="176"/>
     </row>
     <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="178"/>
-      <c r="E100" s="178"/>
-      <c r="F100" s="178"/>
-      <c r="G100" s="178"/>
-      <c r="H100" s="178"/>
-      <c r="I100" s="178"/>
-      <c r="J100" s="178"/>
-      <c r="K100" s="178"/>
-      <c r="L100" s="178"/>
-      <c r="M100" s="178"/>
-      <c r="N100" s="178"/>
-      <c r="O100" s="178"/>
-      <c r="P100" s="178"/>
+      <c r="D100" s="176"/>
+      <c r="E100" s="176"/>
+      <c r="F100" s="176"/>
+      <c r="G100" s="176"/>
+      <c r="H100" s="176"/>
+      <c r="I100" s="176"/>
+      <c r="J100" s="176"/>
+      <c r="K100" s="176"/>
+      <c r="L100" s="176"/>
+      <c r="M100" s="176"/>
+      <c r="N100" s="176"/>
+      <c r="O100" s="176"/>
+      <c r="P100" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="M1:N1"/>
@@ -9213,17 +9224,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/VERGARA/Mayo/vergara MAYO.xlsx
+++ b/VERGARA/Mayo/vergara MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79516097-E447-42D2-A097-56AD91D83CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251F6FB6-B689-4BB7-8E98-CBF927B5A46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="291">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -860,9 +860,6 @@
     <t>Honorarios administracion - Mes de ABRIL - Se debe MAYO</t>
   </si>
   <si>
-    <t>JPL articulos de limpieza - MAYO y ABRIL</t>
-  </si>
-  <si>
     <t>Zaffalon Veronica - Bomba sumergible 075hp 220 vol</t>
   </si>
   <si>
@@ -897,6 +894,12 @@
   </si>
   <si>
     <t>Transf 26/05</t>
+  </si>
+  <si>
+    <t>Transf 27/05</t>
+  </si>
+  <si>
+    <t>Espindola Christian - Tuerca accionadora e instalacion rampa</t>
   </si>
 </sst>
 </file>
@@ -1764,6 +1767,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1797,17 +1812,32 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1824,17 +1854,8 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1844,24 +1865,6 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2287,12 +2290,12 @@
       <c r="A5" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="187" t="s">
+      <c r="B5" s="176" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="187"/>
-      <c r="D5" s="187"/>
-      <c r="E5" s="188"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="177"/>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
@@ -2306,49 +2309,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="190" t="s">
+      <c r="B8" s="179" t="s">
         <v>272</v>
       </c>
-      <c r="C8" s="190"/>
+      <c r="C8" s="179"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="190"/>
-      <c r="C9" s="190"/>
+      <c r="B9" s="179"/>
+      <c r="C9" s="179"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="190"/>
-      <c r="C10" s="190"/>
+      <c r="B10" s="179"/>
+      <c r="C10" s="179"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="189" t="s">
+      <c r="A13" s="178" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
+      <c r="B13" s="178"/>
+      <c r="C13" s="178"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="178"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="189"/>
-      <c r="B14" s="189"/>
-      <c r="C14" s="189"/>
-      <c r="D14" s="189"/>
-      <c r="E14" s="189"/>
+      <c r="A14" s="178"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="178"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="178"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="189"/>
-      <c r="B15" s="189"/>
-      <c r="C15" s="189"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="178"/>
+      <c r="C15" s="178"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="189"/>
-      <c r="B16" s="189"/>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
+      <c r="A16" s="178"/>
+      <c r="B16" s="178"/>
+      <c r="C16" s="178"/>
+      <c r="D16" s="178"/>
+      <c r="E16" s="178"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2717,47 +2720,47 @@
       <c r="E49" s="103"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="178" t="s">
-        <v>285</v>
-      </c>
-      <c r="B50" s="179"/>
+      <c r="A50" s="182" t="s">
+        <v>284</v>
+      </c>
+      <c r="B50" s="183"/>
       <c r="C50" s="65"/>
       <c r="D50" s="168">
         <v>84500</v>
       </c>
       <c r="E50" s="102" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="182" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="178" t="s">
-        <v>285</v>
-      </c>
-      <c r="B51" s="179"/>
+      <c r="B51" s="183"/>
       <c r="C51" s="65"/>
       <c r="D51" s="168">
         <v>262099.86</v>
       </c>
       <c r="E51" s="102" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="180" t="s">
-        <v>282</v>
-      </c>
-      <c r="B52" s="181"/>
+      <c r="A52" s="184" t="s">
+        <v>281</v>
+      </c>
+      <c r="B52" s="185"/>
       <c r="C52" s="55"/>
       <c r="D52" s="168">
         <v>165000</v>
       </c>
       <c r="E52" s="102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="167" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B53" s="145"/>
       <c r="C53" s="55"/>
@@ -2765,12 +2768,12 @@
         <v>450000</v>
       </c>
       <c r="E53" s="102" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="174" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B54" s="175"/>
       <c r="C54" s="55"/>
@@ -2778,12 +2781,12 @@
         <v>230000</v>
       </c>
       <c r="E54" s="102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="156" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B55" s="145"/>
       <c r="C55" s="55"/>
@@ -2791,12 +2794,12 @@
         <v>385000</v>
       </c>
       <c r="E55" s="102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="156" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B56" s="145"/>
       <c r="C56" s="55"/>
@@ -2804,33 +2807,33 @@
         <v>670000</v>
       </c>
       <c r="E56" s="102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="182" t="s">
-        <v>277</v>
-      </c>
-      <c r="B57" s="183"/>
+      <c r="A57" s="186" t="s">
+        <v>290</v>
+      </c>
+      <c r="B57" s="187"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="121">
-        <v>81500</v>
+      <c r="D57" s="168">
+        <v>110000</v>
       </c>
       <c r="E57" s="125" t="s">
-        <v>233</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="182" t="s">
-        <v>288</v>
-      </c>
-      <c r="B58" s="183"/>
+      <c r="A58" s="186" t="s">
+        <v>287</v>
+      </c>
+      <c r="B58" s="187"/>
       <c r="C58" s="5"/>
       <c r="D58" s="170">
         <v>150000</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I58" s="174"/>
       <c r="J58" s="175"/>
@@ -2844,7 +2847,7 @@
       <c r="D59" s="31"/>
       <c r="E59" s="169">
         <f>SUM(D50:D58)</f>
-        <v>2478099.86</v>
+        <v>2506599.86</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2924,7 +2927,7 @@
       <c r="D67" s="117"/>
       <c r="E67" s="154">
         <f>(SUM(E26:E65))</f>
-        <v>5432543.7999999998</v>
+        <v>5461043.7999999998</v>
       </c>
       <c r="F67" s="153"/>
     </row>
@@ -2947,7 +2950,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="174" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B71" s="175"/>
       <c r="C71" s="5"/>
@@ -2978,12 +2981,12 @@
     <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="76" spans="1:7" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="184" t="s">
+      <c r="A76" s="188" t="s">
         <v>263</v>
       </c>
-      <c r="B76" s="185"/>
-      <c r="C76" s="185"/>
-      <c r="D76" s="186"/>
+      <c r="B76" s="189"/>
+      <c r="C76" s="189"/>
+      <c r="D76" s="190"/>
       <c r="E76" s="163">
         <v>1000000</v>
       </c>
@@ -3008,7 +3011,7 @@
       </c>
       <c r="B80" s="91">
         <f>E67</f>
-        <v>5432543.7999999998</v>
+        <v>5461043.7999999998</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3017,7 +3020,7 @@
       </c>
       <c r="B81" s="91">
         <f>E67-E65</f>
-        <v>4809371.8</v>
+        <v>4837871.8</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3154,7 +3157,7 @@
       </c>
       <c r="B97" s="48">
         <f>-B81</f>
-        <v>-4809371.8</v>
+        <v>-4837871.8</v>
       </c>
       <c r="C97" s="21"/>
     </row>
@@ -3194,7 +3197,7 @@
       </c>
       <c r="B101" s="144">
         <f>SUM(B86:B100)</f>
-        <v>-1542647.6253832015</v>
+        <v>-1571147.6253832015</v>
       </c>
       <c r="C101" s="24"/>
       <c r="D101" s="45"/>
@@ -3214,16 +3217,16 @@
       <c r="F103" s="136"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="177" t="s">
+      <c r="A104" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="B104" s="177"/>
-      <c r="C104" s="177"/>
+      <c r="B104" s="181"/>
+      <c r="C104" s="181"/>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="177"/>
-      <c r="B105" s="177"/>
-      <c r="C105" s="177"/>
+      <c r="A105" s="181"/>
+      <c r="B105" s="181"/>
+      <c r="C105" s="181"/>
     </row>
     <row r="106" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="54" t="s">
@@ -3270,43 +3273,35 @@
       <c r="M110" s="8"/>
     </row>
     <row r="111" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="176"/>
-      <c r="B111" s="176"/>
-      <c r="C111" s="176"/>
-      <c r="D111" s="176"/>
-      <c r="E111" s="176"/>
+      <c r="A111" s="180"/>
+      <c r="B111" s="180"/>
+      <c r="C111" s="180"/>
+      <c r="D111" s="180"/>
+      <c r="E111" s="180"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A112" s="176"/>
-      <c r="B112" s="176"/>
-      <c r="C112" s="176"/>
-      <c r="D112" s="176"/>
-      <c r="E112" s="176"/>
+      <c r="A112" s="180"/>
+      <c r="B112" s="180"/>
+      <c r="C112" s="180"/>
+      <c r="D112" s="180"/>
+      <c r="E112" s="180"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="176"/>
-      <c r="B113" s="176"/>
-      <c r="C113" s="176"/>
-      <c r="D113" s="176"/>
-      <c r="E113" s="176"/>
+      <c r="A113" s="180"/>
+      <c r="B113" s="180"/>
+      <c r="C113" s="180"/>
+      <c r="D113" s="180"/>
+      <c r="E113" s="180"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="176"/>
-      <c r="B114" s="176"/>
-      <c r="C114" s="176"/>
-      <c r="D114" s="176"/>
-      <c r="E114" s="176"/>
+      <c r="A114" s="180"/>
+      <c r="B114" s="180"/>
+      <c r="C114" s="180"/>
+      <c r="D114" s="180"/>
+      <c r="E114" s="180"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="A111:E114"/>
     <mergeCell ref="A104:C105"/>
@@ -3318,6 +3313,14 @@
     <mergeCell ref="A76:D76"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3358,10 +3361,10 @@
       <c r="E1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="191">
+      <c r="F1" s="200">
         <v>2102777.02</v>
       </c>
-      <c r="G1" s="191"/>
+      <c r="G1" s="200"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3369,16 +3372,16 @@
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="193">
+      <c r="M1" s="202">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="193"/>
+      <c r="N1" s="202"/>
       <c r="O1" s="157"/>
-      <c r="P1" s="201">
+      <c r="P1" s="207">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="201"/>
+      <c r="Q1" s="207"/>
       <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3391,103 +3394,103 @@
       <c r="E2" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="192">
+      <c r="F2" s="201">
         <v>568429.56999999995</v>
       </c>
-      <c r="G2" s="192"/>
+      <c r="G2" s="201"/>
       <c r="H2" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="I2" s="200">
+      <c r="I2" s="206">
         <v>1000000</v>
       </c>
-      <c r="J2" s="200"/>
+      <c r="J2" s="206"/>
       <c r="K2" s="6" t="s">
         <v>262</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="200">
+      <c r="M2" s="206">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="200"/>
+      <c r="N2" s="206"/>
       <c r="O2" s="159"/>
-      <c r="P2" s="202"/>
-      <c r="Q2" s="202"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="203" t="s">
+      <c r="A3" s="191" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="129"/>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="193" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="196" t="s">
+      <c r="D3" s="193" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="196" t="s">
+      <c r="E3" s="193" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="196" t="s">
+      <c r="F3" s="193" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="198" t="s">
+      <c r="G3" s="195" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="196" t="s">
+      <c r="H3" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="206" t="s">
+      <c r="I3" s="197" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="198" t="s">
+      <c r="J3" s="195" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="198" t="str">
+      <c r="K3" s="195" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="198" t="s">
+      <c r="L3" s="195" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="198" t="s">
+      <c r="M3" s="195" t="s">
         <v>182</v>
       </c>
-      <c r="N3" s="198" t="s">
+      <c r="N3" s="195" t="s">
         <v>183</v>
       </c>
-      <c r="O3" s="198" t="s">
+      <c r="O3" s="195" t="s">
         <v>264</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="194" t="s">
+      <c r="Q3" s="203" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="45"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="204"/>
+      <c r="A4" s="192"/>
       <c r="B4" s="130"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="199"/>
-      <c r="H4" s="205"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="199"/>
-      <c r="M4" s="199"/>
-      <c r="N4" s="199"/>
-      <c r="O4" s="199"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="196"/>
+      <c r="H4" s="194"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="196"/>
+      <c r="K4" s="199"/>
+      <c r="L4" s="196"/>
+      <c r="M4" s="196"/>
+      <c r="N4" s="196"/>
+      <c r="O4" s="196"/>
       <c r="P4" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q4" s="195"/>
+      <c r="Q4" s="204"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="62"/>
@@ -9107,111 +9110,100 @@
       <c r="E93" s="51"/>
     </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="176" t="str">
+      <c r="D95" s="180" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="176"/>
-      <c r="F95" s="176"/>
-      <c r="G95" s="176"/>
-      <c r="H95" s="176"/>
-      <c r="I95" s="176"/>
-      <c r="J95" s="176"/>
-      <c r="K95" s="176"/>
-      <c r="L95" s="176"/>
-      <c r="M95" s="176"/>
-      <c r="N95" s="176"/>
-      <c r="O95" s="176"/>
-      <c r="P95" s="176"/>
+      <c r="E95" s="180"/>
+      <c r="F95" s="180"/>
+      <c r="G95" s="180"/>
+      <c r="H95" s="180"/>
+      <c r="I95" s="180"/>
+      <c r="J95" s="180"/>
+      <c r="K95" s="180"/>
+      <c r="L95" s="180"/>
+      <c r="M95" s="180"/>
+      <c r="N95" s="180"/>
+      <c r="O95" s="180"/>
+      <c r="P95" s="180"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="176"/>
-      <c r="E96" s="176"/>
-      <c r="F96" s="176"/>
-      <c r="G96" s="176"/>
-      <c r="H96" s="176"/>
-      <c r="I96" s="176"/>
-      <c r="J96" s="176"/>
-      <c r="K96" s="176"/>
-      <c r="L96" s="176"/>
-      <c r="M96" s="176"/>
-      <c r="N96" s="176"/>
-      <c r="O96" s="176"/>
-      <c r="P96" s="176"/>
+      <c r="D96" s="180"/>
+      <c r="E96" s="180"/>
+      <c r="F96" s="180"/>
+      <c r="G96" s="180"/>
+      <c r="H96" s="180"/>
+      <c r="I96" s="180"/>
+      <c r="J96" s="180"/>
+      <c r="K96" s="180"/>
+      <c r="L96" s="180"/>
+      <c r="M96" s="180"/>
+      <c r="N96" s="180"/>
+      <c r="O96" s="180"/>
+      <c r="P96" s="180"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="176"/>
-      <c r="E97" s="176"/>
-      <c r="F97" s="176"/>
-      <c r="G97" s="176"/>
-      <c r="H97" s="176"/>
-      <c r="I97" s="176"/>
-      <c r="J97" s="176"/>
-      <c r="K97" s="176"/>
-      <c r="L97" s="176"/>
-      <c r="M97" s="176"/>
-      <c r="N97" s="176"/>
-      <c r="O97" s="176"/>
-      <c r="P97" s="176"/>
+      <c r="D97" s="180"/>
+      <c r="E97" s="180"/>
+      <c r="F97" s="180"/>
+      <c r="G97" s="180"/>
+      <c r="H97" s="180"/>
+      <c r="I97" s="180"/>
+      <c r="J97" s="180"/>
+      <c r="K97" s="180"/>
+      <c r="L97" s="180"/>
+      <c r="M97" s="180"/>
+      <c r="N97" s="180"/>
+      <c r="O97" s="180"/>
+      <c r="P97" s="180"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="176"/>
-      <c r="E98" s="176"/>
-      <c r="F98" s="176"/>
-      <c r="G98" s="176"/>
-      <c r="H98" s="176"/>
-      <c r="I98" s="176"/>
-      <c r="J98" s="176"/>
-      <c r="K98" s="176"/>
-      <c r="L98" s="176"/>
-      <c r="M98" s="176"/>
-      <c r="N98" s="176"/>
-      <c r="O98" s="176"/>
-      <c r="P98" s="176"/>
+      <c r="D98" s="180"/>
+      <c r="E98" s="180"/>
+      <c r="F98" s="180"/>
+      <c r="G98" s="180"/>
+      <c r="H98" s="180"/>
+      <c r="I98" s="180"/>
+      <c r="J98" s="180"/>
+      <c r="K98" s="180"/>
+      <c r="L98" s="180"/>
+      <c r="M98" s="180"/>
+      <c r="N98" s="180"/>
+      <c r="O98" s="180"/>
+      <c r="P98" s="180"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="176"/>
-      <c r="E99" s="176"/>
-      <c r="F99" s="176"/>
-      <c r="G99" s="176"/>
-      <c r="H99" s="176"/>
-      <c r="I99" s="176"/>
-      <c r="J99" s="176"/>
-      <c r="K99" s="176"/>
-      <c r="L99" s="176"/>
-      <c r="M99" s="176"/>
-      <c r="N99" s="176"/>
-      <c r="O99" s="176"/>
-      <c r="P99" s="176"/>
+      <c r="D99" s="180"/>
+      <c r="E99" s="180"/>
+      <c r="F99" s="180"/>
+      <c r="G99" s="180"/>
+      <c r="H99" s="180"/>
+      <c r="I99" s="180"/>
+      <c r="J99" s="180"/>
+      <c r="K99" s="180"/>
+      <c r="L99" s="180"/>
+      <c r="M99" s="180"/>
+      <c r="N99" s="180"/>
+      <c r="O99" s="180"/>
+      <c r="P99" s="180"/>
     </row>
     <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="176"/>
-      <c r="E100" s="176"/>
-      <c r="F100" s="176"/>
-      <c r="G100" s="176"/>
-      <c r="H100" s="176"/>
-      <c r="I100" s="176"/>
-      <c r="J100" s="176"/>
-      <c r="K100" s="176"/>
-      <c r="L100" s="176"/>
-      <c r="M100" s="176"/>
-      <c r="N100" s="176"/>
-      <c r="O100" s="176"/>
-      <c r="P100" s="176"/>
+      <c r="D100" s="180"/>
+      <c r="E100" s="180"/>
+      <c r="F100" s="180"/>
+      <c r="G100" s="180"/>
+      <c r="H100" s="180"/>
+      <c r="I100" s="180"/>
+      <c r="J100" s="180"/>
+      <c r="K100" s="180"/>
+      <c r="L100" s="180"/>
+      <c r="M100" s="180"/>
+      <c r="N100" s="180"/>
+      <c r="O100" s="180"/>
+      <c r="P100" s="180"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="M1:N1"/>
@@ -9224,6 +9216,17 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/VERGARA/Mayo/vergara MAYO.xlsx
+++ b/VERGARA/Mayo/vergara MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8545EB19-B4BE-46AD-ADC0-728153309E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AAED02-C6CA-4BA8-96CB-0786DCB374B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="289">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -891,6 +891,9 @@
   </si>
   <si>
     <t>Santiago Tarragosa</t>
+  </si>
+  <si>
+    <t>HABIA PAGADO LOS 5300, SU DEUDA DEBE ESTAR EN 0</t>
   </si>
 </sst>
 </file>
@@ -898,15 +901,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1511,10 +1514,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1522,7 +1525,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1535,8 +1538,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1545,31 +1548,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1580,8 +1583,8 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1602,19 +1605,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1635,35 +1638,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1671,12 +1674,12 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1687,18 +1690,18 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1714,27 +1717,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1744,7 +1747,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1752,51 +1755,48 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1825,16 +1825,37 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1842,6 +1863,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1852,42 +1891,9 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="24" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2255,20 +2261,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="68" t="s">
         <v>180</v>
@@ -2277,7 +2283,7 @@
       <c r="D1" s="68"/>
       <c r="E1" s="69"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="136" t="s">
         <v>31</v>
@@ -2286,7 +2292,7 @@
       <c r="D2" s="136"/>
       <c r="E2" s="70"/>
     </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
       <c r="B3" s="137" t="s">
         <v>213</v>
@@ -2297,7 +2303,7 @@
       </c>
       <c r="E3" s="70"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2308,18 +2314,18 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="185" t="s">
+      <c r="B5" s="199" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="186"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="200"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>190</v>
       </c>
@@ -2330,57 +2336,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="188" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="202" t="s">
         <v>248</v>
       </c>
-      <c r="C8" s="188"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="188"/>
-      <c r="C9" s="188"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="187" t="s">
+      <c r="C8" s="202"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="202"/>
+      <c r="C9" s="202"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="202"/>
+      <c r="C10" s="202"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="201" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="187"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="187"/>
-      <c r="E13" s="187"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="187"/>
-      <c r="B14" s="187"/>
-      <c r="C14" s="187"/>
-      <c r="D14" s="187"/>
-      <c r="E14" s="187"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="187"/>
-      <c r="B15" s="187"/>
-      <c r="C15" s="187"/>
-      <c r="D15" s="187"/>
-      <c r="E15" s="187"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="187"/>
-      <c r="B16" s="187"/>
-      <c r="C16" s="187"/>
-      <c r="D16" s="187"/>
-      <c r="E16" s="187"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="201"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="201"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="201"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="201"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="201"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>11</v>
       </c>
@@ -2389,7 +2395,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="33" t="s">
         <v>37</v>
       </c>
@@ -2398,42 +2404,42 @@
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>188</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="217">
+      <c r="D22" s="184">
         <v>598522.19999999995</v>
       </c>
       <c r="E22" s="90"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>186</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="217">
+      <c r="D23" s="184">
         <v>-139605.89000000001</v>
       </c>
       <c r="E23" s="90"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>187</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="217">
+      <c r="D24" s="184">
         <v>0.69</v>
       </c>
       <c r="E24" s="90"/>
       <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="56" t="s">
         <v>38</v>
       </c>
@@ -2446,7 +2452,7 @@
       <c r="E25" s="91"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="26" t="s">
         <v>1</v>
       </c>
@@ -2459,7 +2465,7 @@
       </c>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="33" t="s">
         <v>23</v>
       </c>
@@ -2468,33 +2474,33 @@
       <c r="D27" s="34"/>
       <c r="E27" s="93"/>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183" t="s">
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="188" t="s">
         <v>250</v>
       </c>
-      <c r="B28" s="184"/>
+      <c r="B28" s="189"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="217">
+      <c r="D28" s="184">
         <v>31000</v>
       </c>
       <c r="E28" s="94" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="183" t="s">
+    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="188" t="s">
         <v>252</v>
       </c>
-      <c r="B29" s="184"/>
+      <c r="B29" s="189"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="217">
+      <c r="D29" s="184">
         <v>470000</v>
       </c>
       <c r="E29" s="94" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="26" t="s">
         <v>17</v>
       </c>
@@ -2506,7 +2512,7 @@
         <v>501000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="31" t="s">
         <v>34</v>
       </c>
@@ -2515,30 +2521,30 @@
       <c r="D31" s="35"/>
       <c r="E31" s="67"/>
     </row>
-    <row r="32" spans="1:7" s="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="160" t="s">
         <v>277</v>
       </c>
       <c r="B32" s="154"/>
       <c r="C32" s="54"/>
-      <c r="D32" s="218">
+      <c r="D32" s="185">
         <v>70868</v>
       </c>
       <c r="E32" s="118"/>
       <c r="G32" s="159"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="183" t="s">
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="188" t="s">
         <v>278</v>
       </c>
-      <c r="B33" s="184"/>
+      <c r="B33" s="189"/>
       <c r="C33" s="54"/>
-      <c r="D33" s="219">
+      <c r="D33" s="186">
         <v>719.9</v>
       </c>
       <c r="E33" s="118"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="26" t="s">
         <v>2</v>
       </c>
@@ -2550,7 +2556,7 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>18</v>
       </c>
@@ -2559,13 +2565,13 @@
       <c r="D35" s="38"/>
       <c r="E35" s="97"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="53"/>
-      <c r="D36" s="220">
+      <c r="D36" s="187">
         <v>295029.98</v>
       </c>
       <c r="E36" s="120" t="s">
@@ -2573,7 +2579,7 @@
       </c>
       <c r="G36" s="125"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>251</v>
       </c>
@@ -2588,7 +2594,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="str">
         <f>A37</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2605,7 +2611,7 @@
         <v>Debito 12/05</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="str">
         <f>A38</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2622,7 +2628,7 @@
         <v>Debito 12/05</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26" t="s">
         <v>3</v>
       </c>
@@ -2634,7 +2640,7 @@
         <v>374947.26999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>20</v>
       </c>
@@ -2643,7 +2649,7 @@
       <c r="D41" s="38"/>
       <c r="E41" s="97"/>
     </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>185</v>
       </c>
@@ -2652,7 +2658,7 @@
       <c r="D42" s="117"/>
       <c r="E42" s="103"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>273</v>
       </c>
@@ -2665,11 +2671,11 @@
         <v>274</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="183" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="188" t="s">
         <v>222</v>
       </c>
-      <c r="B44" s="184"/>
+      <c r="B44" s="189"/>
       <c r="C44" s="5"/>
       <c r="D44" s="117">
         <v>81423.929999999993</v>
@@ -2678,7 +2684,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="26" t="s">
         <v>4</v>
       </c>
@@ -2690,7 +2696,7 @@
         <v>131423.93</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>19</v>
       </c>
@@ -2699,11 +2705,11 @@
       <c r="D46" s="37"/>
       <c r="E46" s="99"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="191" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="192" t="s">
         <v>271</v>
       </c>
-      <c r="B47" s="192"/>
+      <c r="B47" s="193"/>
       <c r="C47" s="65"/>
       <c r="D47" s="117">
         <v>84500</v>
@@ -2712,11 +2718,11 @@
         <v>259</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="191" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="192" t="s">
         <v>272</v>
       </c>
-      <c r="B48" s="192"/>
+      <c r="B48" s="193"/>
       <c r="C48" s="65"/>
       <c r="D48" s="117">
         <v>262099.86</v>
@@ -2726,7 +2732,7 @@
       </c>
       <c r="G48" s="140"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="155" t="s">
         <v>270</v>
       </c>
@@ -2739,7 +2745,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="155" t="s">
         <v>275</v>
       </c>
@@ -2752,11 +2758,11 @@
         <v>276</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="183" t="s">
+    <row r="51" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="188" t="s">
         <v>257</v>
       </c>
-      <c r="B51" s="184"/>
+      <c r="B51" s="189"/>
       <c r="C51" s="55"/>
       <c r="D51" s="117">
         <v>165000</v>
@@ -2765,11 +2771,11 @@
         <v>254</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="183" t="s">
+    <row r="52" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="188" t="s">
         <v>281</v>
       </c>
-      <c r="B52" s="184"/>
+      <c r="B52" s="189"/>
       <c r="C52" s="55"/>
       <c r="D52" s="117">
         <v>450000</v>
@@ -2778,11 +2784,11 @@
         <v>260</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="183" t="s">
+    <row r="53" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="188" t="s">
         <v>256</v>
       </c>
-      <c r="B53" s="184"/>
+      <c r="B53" s="189"/>
       <c r="C53" s="55"/>
       <c r="D53" s="117">
         <v>230000</v>
@@ -2791,7 +2797,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="143" t="s">
         <v>255</v>
       </c>
@@ -2804,11 +2810,11 @@
         <v>254</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="183" t="s">
+    <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="188" t="s">
         <v>282</v>
       </c>
-      <c r="B55" s="184"/>
+      <c r="B55" s="189"/>
       <c r="C55" s="55"/>
       <c r="D55" s="117">
         <v>135000</v>
@@ -2817,7 +2823,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="143" t="s">
         <v>253</v>
       </c>
@@ -2830,11 +2836,11 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="193" t="s">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="194" t="s">
         <v>264</v>
       </c>
-      <c r="B57" s="194"/>
+      <c r="B57" s="195"/>
       <c r="C57" s="5"/>
       <c r="D57" s="117">
         <v>110000</v>
@@ -2843,11 +2849,11 @@
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="183" t="s">
+    <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="188" t="s">
         <v>261</v>
       </c>
-      <c r="B58" s="184"/>
+      <c r="B58" s="189"/>
       <c r="C58" s="5"/>
       <c r="D58" s="101">
         <v>150000</v>
@@ -2855,10 +2861,10 @@
       <c r="E58" s="157" t="s">
         <v>262</v>
       </c>
-      <c r="I58" s="183"/>
-      <c r="J58" s="184"/>
-    </row>
-    <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="188"/>
+      <c r="J58" s="189"/>
+    </row>
+    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="26" t="s">
         <v>10</v>
       </c>
@@ -2870,7 +2876,7 @@
         <v>2702899.86</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="33" t="s">
         <v>13</v>
       </c>
@@ -2879,7 +2885,7 @@
       <c r="D60" s="28"/>
       <c r="E60" s="99"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>216</v>
       </c>
@@ -2891,7 +2897,7 @@
       </c>
       <c r="E61" s="107"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>217</v>
       </c>
@@ -2902,7 +2908,7 @@
       </c>
       <c r="E62" s="104"/>
     </row>
-    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="52" t="s">
         <v>17</v>
       </c>
@@ -2914,14 +2920,14 @@
         <v>168465.71000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="90"/>
       <c r="E64" s="109"/>
     </row>
-    <row r="65" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="29" t="s">
         <v>240</v>
       </c>
@@ -2930,14 +2936,14 @@
       <c r="D65" s="110"/>
       <c r="E65" s="142"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="D66" s="111"/>
       <c r="E66" s="112"/>
       <c r="F66" s="45"/>
       <c r="G66" s="149"/>
     </row>
-    <row r="67" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>14</v>
       </c>
@@ -2950,15 +2956,15 @@
       </c>
       <c r="F67" s="140"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D68" s="111"/>
       <c r="E68" s="111"/>
     </row>
-    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D69" s="111"/>
       <c r="E69" s="111"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
         <v>45</v>
       </c>
@@ -2967,11 +2973,11 @@
       <c r="D70" s="114"/>
       <c r="E70" s="115"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="183" t="s">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="188" t="s">
         <v>258</v>
       </c>
-      <c r="B71" s="184"/>
+      <c r="B71" s="189"/>
       <c r="C71" s="5"/>
       <c r="D71" s="101">
         <v>304993.06</v>
@@ -2980,14 +2986,14 @@
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="100"/>
       <c r="B72" s="102"/>
       <c r="C72" s="5"/>
       <c r="D72" s="101"/>
       <c r="E72" s="98"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="50"/>
       <c r="B73" s="49"/>
       <c r="C73" s="49"/>
@@ -2997,19 +3003,19 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="195" t="s">
+    <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="196" t="s">
         <v>279</v>
       </c>
-      <c r="B76" s="196"/>
-      <c r="C76" s="196"/>
-      <c r="D76" s="197"/>
+      <c r="B76" s="197"/>
+      <c r="C76" s="197"/>
+      <c r="D76" s="198"/>
       <c r="E76" s="150"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>24</v>
       </c>
@@ -3021,8 +3027,8 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="87" t="s">
         <v>15</v>
       </c>
@@ -3031,7 +3037,7 @@
         <v>4409241.67</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="87" t="s">
         <v>16</v>
       </c>
@@ -3040,7 +3046,7 @@
         <v>4409241.67</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="87" t="s">
         <v>25</v>
       </c>
@@ -3049,7 +3055,7 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="87" t="s">
         <v>41</v>
       </c>
@@ -3058,15 +3064,15 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="46" t="s">
         <v>36</v>
       </c>
       <c r="B85" s="126"/>
       <c r="C85" s="21"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="30" t="s">
         <v>179</v>
       </c>
@@ -3075,7 +3081,7 @@
       </c>
       <c r="C86" s="23"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
         <v>9</v>
       </c>
@@ -3085,7 +3091,7 @@
       </c>
       <c r="C87" s="21"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>43</v>
       </c>
@@ -3095,8 +3101,8 @@
       </c>
       <c r="C88" s="21"/>
     </row>
-    <row r="89" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="216" t="s">
+    <row r="89" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="183" t="s">
         <v>286</v>
       </c>
       <c r="B89" s="48">
@@ -3105,7 +3111,7 @@
       </c>
       <c r="C89" s="21"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
         <v>285</v>
       </c>
@@ -3114,7 +3120,7 @@
       </c>
       <c r="C90" s="21"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="121" t="s">
         <v>46</v>
       </c>
@@ -3123,7 +3129,7 @@
       </c>
       <c r="C91" s="21"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="41" t="s">
         <v>26</v>
       </c>
@@ -3133,7 +3139,7 @@
       </c>
       <c r="C92" s="21"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="41" t="s">
         <v>218</v>
       </c>
@@ -3143,7 +3149,7 @@
       </c>
       <c r="C93" s="21"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="41" t="s">
         <v>219</v>
       </c>
@@ -3153,7 +3159,7 @@
       </c>
       <c r="C94" s="21"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="25" t="s">
         <v>27</v>
       </c>
@@ -3163,7 +3169,7 @@
       </c>
       <c r="C95" s="21"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="130" t="s">
         <v>10</v>
       </c>
@@ -3174,52 +3180,52 @@
       <c r="C96" s="24"/>
       <c r="D96" s="45"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B97" s="43"/>
       <c r="C97" s="24"/>
       <c r="D97" s="45"/>
       <c r="E97" s="127"/>
       <c r="F97" s="128"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B98" s="43"/>
       <c r="C98" s="24"/>
       <c r="D98" s="45"/>
       <c r="E98" s="127"/>
       <c r="F98" s="128"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="190" t="s">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="190"/>
-      <c r="C99" s="190"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="190"/>
-      <c r="B100" s="190"/>
-      <c r="C100" s="190"/>
-    </row>
-    <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="191"/>
+      <c r="C99" s="191"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="191"/>
+      <c r="B100" s="191"/>
+      <c r="C100" s="191"/>
+    </row>
+    <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="54"/>
       <c r="B101" s="145"/>
       <c r="C101" s="36">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="54"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
     </row>
-    <row r="103" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="134"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36">
         <v>61209</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="46" t="s">
         <v>10</v>
       </c>
@@ -3229,39 +3235,46 @@
       </c>
       <c r="C104" s="47"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M105" s="8"/>
     </row>
-    <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="189"/>
-      <c r="B106" s="189"/>
-      <c r="C106" s="189"/>
-      <c r="D106" s="189"/>
-      <c r="E106" s="189"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="189"/>
-      <c r="B107" s="189"/>
-      <c r="C107" s="189"/>
-      <c r="D107" s="189"/>
-      <c r="E107" s="189"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="189"/>
-      <c r="B108" s="189"/>
-      <c r="C108" s="189"/>
-      <c r="D108" s="189"/>
-      <c r="E108" s="189"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="189"/>
-      <c r="B109" s="189"/>
-      <c r="C109" s="189"/>
-      <c r="D109" s="189"/>
-      <c r="E109" s="189"/>
+    <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="190"/>
+      <c r="B106" s="190"/>
+      <c r="C106" s="190"/>
+      <c r="D106" s="190"/>
+      <c r="E106" s="190"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="190"/>
+      <c r="B107" s="190"/>
+      <c r="C107" s="190"/>
+      <c r="D107" s="190"/>
+      <c r="E107" s="190"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" s="190"/>
+      <c r="B108" s="190"/>
+      <c r="C108" s="190"/>
+      <c r="D108" s="190"/>
+      <c r="E108" s="190"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="190"/>
+      <c r="B109" s="190"/>
+      <c r="C109" s="190"/>
+      <c r="D109" s="190"/>
+      <c r="E109" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="A106:E109"/>
     <mergeCell ref="A99:C100"/>
@@ -3275,13 +3288,6 @@
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3292,27 +3298,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3320,10 +3326,10 @@
       <c r="E1" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="207">
+      <c r="F1" s="203">
         <v>2102777.02</v>
       </c>
-      <c r="G1" s="207"/>
+      <c r="G1" s="203"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3331,19 +3337,19 @@
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="209">
+      <c r="M1" s="205">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="209"/>
+      <c r="N1" s="205"/>
       <c r="O1" s="144"/>
-      <c r="P1" s="214">
+      <c r="P1" s="213">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="214"/>
+      <c r="Q1" s="213"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3351,105 +3357,105 @@
       <c r="E2" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="208">
+      <c r="F2" s="204">
         <v>568429.56999999995</v>
       </c>
-      <c r="G2" s="208"/>
+      <c r="G2" s="204"/>
       <c r="H2" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="I2" s="213">
+      <c r="I2" s="212">
         <v>1200000</v>
       </c>
-      <c r="J2" s="213"/>
+      <c r="J2" s="212"/>
       <c r="K2" s="6" t="s">
         <v>241</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="213">
+      <c r="M2" s="212">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="213"/>
+      <c r="N2" s="212"/>
       <c r="O2" s="146"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="215"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="198" t="s">
+      <c r="P2" s="214"/>
+      <c r="Q2" s="214"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="215" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="122"/>
-      <c r="C3" s="200" t="s">
+      <c r="C3" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="200" t="s">
+      <c r="D3" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="200" t="s">
+      <c r="E3" s="208" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="200" t="s">
+      <c r="F3" s="208" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="202" t="s">
+      <c r="G3" s="210" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="200" t="s">
+      <c r="H3" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="204" t="s">
+      <c r="I3" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="202" t="s">
+      <c r="J3" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="202" t="str">
+      <c r="K3" s="210" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="202" t="s">
+      <c r="L3" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="202" t="s">
+      <c r="M3" s="210" t="s">
         <v>181</v>
       </c>
-      <c r="N3" s="202" t="s">
+      <c r="N3" s="210" t="s">
         <v>182</v>
       </c>
-      <c r="O3" s="202" t="s">
+      <c r="O3" s="210" t="s">
         <v>242</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="210" t="s">
+      <c r="Q3" s="206" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="45"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="199"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="216"/>
       <c r="B4" s="123"/>
-      <c r="C4" s="201"/>
-      <c r="D4" s="201"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="205"/>
-      <c r="J4" s="203"/>
-      <c r="K4" s="206"/>
-      <c r="L4" s="203"/>
-      <c r="M4" s="203"/>
-      <c r="N4" s="203"/>
-      <c r="O4" s="203"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="219"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="211"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
       <c r="P4" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q4" s="211"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="207"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="62"/>
       <c r="B5" s="62" t="s">
         <v>48</v>
@@ -3512,7 +3518,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="62"/>
       <c r="B6" s="62" t="s">
         <v>50</v>
@@ -3576,7 +3582,7 @@
       </c>
       <c r="S6" s="45"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="62">
         <v>1</v>
       </c>
@@ -3640,7 +3646,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="62">
         <v>2</v>
       </c>
@@ -3703,7 +3709,7 @@
       </c>
       <c r="T8" s="45"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="62">
         <v>3</v>
       </c>
@@ -3771,7 +3777,7 @@
       </c>
       <c r="T9" s="45"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="62">
         <v>4</v>
       </c>
@@ -3838,7 +3844,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="62">
         <v>5</v>
       </c>
@@ -3903,7 +3909,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="62">
         <v>6</v>
       </c>
@@ -3968,7 +3974,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="62">
         <v>7</v>
       </c>
@@ -4035,7 +4041,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="62">
         <v>8</v>
       </c>
@@ -4102,7 +4108,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="62">
         <v>1</v>
       </c>
@@ -4169,7 +4175,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="62">
         <v>1</v>
       </c>
@@ -4236,7 +4242,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="62">
         <v>2</v>
       </c>
@@ -4303,7 +4309,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="62">
         <v>2</v>
       </c>
@@ -4370,7 +4376,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="62">
         <v>3</v>
       </c>
@@ -4439,7 +4445,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="62">
         <v>3</v>
       </c>
@@ -4510,7 +4516,7 @@
       </c>
       <c r="T20" s="44"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62">
         <v>4</v>
       </c>
@@ -4577,7 +4583,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="62">
         <v>4</v>
       </c>
@@ -4639,7 +4645,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="62">
         <v>5</v>
       </c>
@@ -4703,7 +4709,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="62">
         <v>5</v>
       </c>
@@ -4770,7 +4776,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="62">
         <v>6</v>
       </c>
@@ -4834,7 +4840,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="62">
         <v>6</v>
       </c>
@@ -4901,7 +4907,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="62">
         <v>7</v>
       </c>
@@ -4968,7 +4974,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="62">
         <v>7</v>
       </c>
@@ -5035,7 +5041,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="62">
         <v>8</v>
       </c>
@@ -5100,7 +5106,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="62">
         <v>8</v>
       </c>
@@ -5167,7 +5173,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="62">
         <v>9</v>
       </c>
@@ -5232,7 +5238,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="62">
         <v>9</v>
       </c>
@@ -5298,7 +5304,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="62">
         <v>10</v>
       </c>
@@ -5363,7 +5369,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="62">
         <v>10</v>
       </c>
@@ -5430,7 +5436,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="62">
         <v>11</v>
       </c>
@@ -5497,7 +5503,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="62">
         <v>11</v>
       </c>
@@ -5564,7 +5570,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="62">
         <v>12</v>
       </c>
@@ -5631,7 +5637,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="62">
         <v>12</v>
       </c>
@@ -5695,7 +5701,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="62">
         <v>1</v>
       </c>
@@ -5762,7 +5768,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="62">
         <v>1</v>
       </c>
@@ -5830,7 +5836,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="61">
         <v>1</v>
       </c>
@@ -5896,7 +5902,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="62">
         <v>2</v>
       </c>
@@ -5963,7 +5969,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62">
         <v>2</v>
       </c>
@@ -6027,7 +6033,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="62">
         <v>2</v>
       </c>
@@ -6091,7 +6097,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="62">
         <v>3</v>
       </c>
@@ -6155,7 +6161,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="62">
         <v>3</v>
       </c>
@@ -6222,7 +6228,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="62">
         <v>3</v>
       </c>
@@ -6290,7 +6296,7 @@
       </c>
       <c r="T47" s="152"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="62">
         <v>4</v>
       </c>
@@ -6357,7 +6363,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="62">
         <v>4</v>
       </c>
@@ -6424,7 +6430,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="62">
         <v>4</v>
       </c>
@@ -6488,7 +6494,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="62">
         <v>5</v>
       </c>
@@ -6553,7 +6559,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="62">
         <v>5</v>
       </c>
@@ -6620,7 +6626,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="62">
         <v>5</v>
       </c>
@@ -6687,7 +6693,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="62">
         <v>6</v>
       </c>
@@ -6752,7 +6758,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="62">
         <v>6</v>
       </c>
@@ -6816,7 +6822,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="62">
         <v>6</v>
       </c>
@@ -6881,7 +6887,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="62">
         <v>7</v>
       </c>
@@ -6917,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="62">
         <v>7</v>
       </c>
@@ -6953,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="62">
         <v>7</v>
       </c>
@@ -7020,7 +7026,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="62">
         <v>8</v>
       </c>
@@ -7082,7 +7088,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="62">
         <v>8</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="62">
         <v>8</v>
       </c>
@@ -7206,7 +7212,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="62">
         <v>9</v>
       </c>
@@ -7273,7 +7279,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="62">
         <v>9</v>
       </c>
@@ -7335,7 +7341,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="62">
         <v>9</v>
       </c>
@@ -7402,7 +7408,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="62">
         <v>10</v>
       </c>
@@ -7467,7 +7473,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="62">
         <v>10</v>
       </c>
@@ -7533,7 +7539,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="62">
         <v>10</v>
       </c>
@@ -7597,7 +7603,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="62">
         <v>11</v>
       </c>
@@ -7659,7 +7665,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="62">
         <v>11</v>
       </c>
@@ -7721,7 +7727,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="62">
         <v>11</v>
       </c>
@@ -7787,7 +7793,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="62"/>
       <c r="B72" s="81" t="s">
         <v>156</v>
@@ -7852,7 +7858,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="62"/>
       <c r="B73" s="81" t="s">
         <v>157</v>
@@ -7912,7 +7918,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="62"/>
       <c r="B74" s="81" t="s">
         <v>158</v>
@@ -7972,7 +7978,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="62"/>
       <c r="B75" s="81" t="s">
         <v>160</v>
@@ -8032,7 +8038,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="62"/>
       <c r="B76" s="81" t="s">
         <v>161</v>
@@ -8095,7 +8101,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="62"/>
       <c r="B77" s="81" t="s">
         <v>162</v>
@@ -8158,7 +8164,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="62"/>
       <c r="B78" s="81" t="s">
         <v>164</v>
@@ -8221,7 +8227,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="62"/>
       <c r="B79" s="81" t="s">
         <v>165</v>
@@ -8283,7 +8289,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="62"/>
       <c r="B80" s="81" t="s">
         <v>166</v>
@@ -8303,11 +8309,11 @@
       <c r="G80" s="72">
         <v>105752.06</v>
       </c>
-      <c r="H80" s="124">
+      <c r="H80" s="221">
         <f>100452.06</f>
         <v>100452.06</v>
       </c>
-      <c r="I80" s="73">
+      <c r="I80" s="222">
         <f t="shared" si="13"/>
         <v>5300</v>
       </c>
@@ -8347,8 +8353,11 @@
         <f t="shared" si="22"/>
         <v>0.06</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S80" s="223" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="62">
         <v>12</v>
       </c>
@@ -8410,7 +8419,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="62">
         <v>12</v>
       </c>
@@ -8472,7 +8481,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="62">
         <v>12</v>
       </c>
@@ -8537,7 +8546,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="62"/>
       <c r="B84" s="80" t="s">
         <v>171</v>
@@ -8597,7 +8606,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="62"/>
       <c r="B85" s="80" t="s">
         <v>172</v>
@@ -8662,7 +8671,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="62"/>
       <c r="B86" s="80" t="s">
         <v>173</v>
@@ -8727,7 +8736,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="62"/>
       <c r="B87" s="62" t="s">
         <v>174</v>
@@ -8790,7 +8799,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="62"/>
       <c r="B88" s="62" t="s">
         <v>175</v>
@@ -8852,7 +8861,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="62"/>
       <c r="B89" s="62" t="s">
         <v>176</v>
@@ -8918,7 +8927,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="61"/>
       <c r="B90" s="61" t="s">
         <v>177</v>
@@ -8980,7 +8989,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="62"/>
       <c r="B91" s="147"/>
       <c r="C91" s="147"/>
@@ -9000,7 +9009,7 @@
       <c r="Q91" s="170"/>
       <c r="R91" s="45"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="85"/>
       <c r="B92" s="171"/>
       <c r="C92" s="172"/>
@@ -9055,105 +9064,116 @@
         <v>13568044.699999999</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
     </row>
-    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="189" t="str">
+    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D95" s="190" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="189"/>
-      <c r="F95" s="189"/>
-      <c r="G95" s="189"/>
-      <c r="H95" s="189"/>
-      <c r="I95" s="189"/>
-      <c r="J95" s="189"/>
-      <c r="K95" s="189"/>
-      <c r="L95" s="189"/>
-      <c r="M95" s="189"/>
-      <c r="N95" s="189"/>
-      <c r="O95" s="189"/>
-      <c r="P95" s="189"/>
-    </row>
-    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="189"/>
-      <c r="E96" s="189"/>
-      <c r="F96" s="189"/>
-      <c r="G96" s="189"/>
-      <c r="H96" s="189"/>
-      <c r="I96" s="189"/>
-      <c r="J96" s="189"/>
-      <c r="K96" s="189"/>
-      <c r="L96" s="189"/>
-      <c r="M96" s="189"/>
-      <c r="N96" s="189"/>
-      <c r="O96" s="189"/>
-      <c r="P96" s="189"/>
-    </row>
-    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="189"/>
-      <c r="E97" s="189"/>
-      <c r="F97" s="189"/>
-      <c r="G97" s="189"/>
-      <c r="H97" s="189"/>
-      <c r="I97" s="189"/>
-      <c r="J97" s="189"/>
-      <c r="K97" s="189"/>
-      <c r="L97" s="189"/>
-      <c r="M97" s="189"/>
-      <c r="N97" s="189"/>
-      <c r="O97" s="189"/>
-      <c r="P97" s="189"/>
-    </row>
-    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="189"/>
-      <c r="E98" s="189"/>
-      <c r="F98" s="189"/>
-      <c r="G98" s="189"/>
-      <c r="H98" s="189"/>
-      <c r="I98" s="189"/>
-      <c r="J98" s="189"/>
-      <c r="K98" s="189"/>
-      <c r="L98" s="189"/>
-      <c r="M98" s="189"/>
-      <c r="N98" s="189"/>
-      <c r="O98" s="189"/>
-      <c r="P98" s="189"/>
-    </row>
-    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="189"/>
-      <c r="E99" s="189"/>
-      <c r="F99" s="189"/>
-      <c r="G99" s="189"/>
-      <c r="H99" s="189"/>
-      <c r="I99" s="189"/>
-      <c r="J99" s="189"/>
-      <c r="K99" s="189"/>
-      <c r="L99" s="189"/>
-      <c r="M99" s="189"/>
-      <c r="N99" s="189"/>
-      <c r="O99" s="189"/>
-      <c r="P99" s="189"/>
-    </row>
-    <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="189"/>
-      <c r="E100" s="189"/>
-      <c r="F100" s="189"/>
-      <c r="G100" s="189"/>
-      <c r="H100" s="189"/>
-      <c r="I100" s="189"/>
-      <c r="J100" s="189"/>
-      <c r="K100" s="189"/>
-      <c r="L100" s="189"/>
-      <c r="M100" s="189"/>
-      <c r="N100" s="189"/>
-      <c r="O100" s="189"/>
-      <c r="P100" s="189"/>
+      <c r="E95" s="190"/>
+      <c r="F95" s="190"/>
+      <c r="G95" s="190"/>
+      <c r="H95" s="190"/>
+      <c r="I95" s="190"/>
+      <c r="J95" s="190"/>
+      <c r="K95" s="190"/>
+      <c r="L95" s="190"/>
+      <c r="M95" s="190"/>
+      <c r="N95" s="190"/>
+      <c r="O95" s="190"/>
+      <c r="P95" s="190"/>
+    </row>
+    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D96" s="190"/>
+      <c r="E96" s="190"/>
+      <c r="F96" s="190"/>
+      <c r="G96" s="190"/>
+      <c r="H96" s="190"/>
+      <c r="I96" s="190"/>
+      <c r="J96" s="190"/>
+      <c r="K96" s="190"/>
+      <c r="L96" s="190"/>
+      <c r="M96" s="190"/>
+      <c r="N96" s="190"/>
+      <c r="O96" s="190"/>
+      <c r="P96" s="190"/>
+    </row>
+    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D97" s="190"/>
+      <c r="E97" s="190"/>
+      <c r="F97" s="190"/>
+      <c r="G97" s="190"/>
+      <c r="H97" s="190"/>
+      <c r="I97" s="190"/>
+      <c r="J97" s="190"/>
+      <c r="K97" s="190"/>
+      <c r="L97" s="190"/>
+      <c r="M97" s="190"/>
+      <c r="N97" s="190"/>
+      <c r="O97" s="190"/>
+      <c r="P97" s="190"/>
+    </row>
+    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D98" s="190"/>
+      <c r="E98" s="190"/>
+      <c r="F98" s="190"/>
+      <c r="G98" s="190"/>
+      <c r="H98" s="190"/>
+      <c r="I98" s="190"/>
+      <c r="J98" s="190"/>
+      <c r="K98" s="190"/>
+      <c r="L98" s="190"/>
+      <c r="M98" s="190"/>
+      <c r="N98" s="190"/>
+      <c r="O98" s="190"/>
+      <c r="P98" s="190"/>
+    </row>
+    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D99" s="190"/>
+      <c r="E99" s="190"/>
+      <c r="F99" s="190"/>
+      <c r="G99" s="190"/>
+      <c r="H99" s="190"/>
+      <c r="I99" s="190"/>
+      <c r="J99" s="190"/>
+      <c r="K99" s="190"/>
+      <c r="L99" s="190"/>
+      <c r="M99" s="190"/>
+      <c r="N99" s="190"/>
+      <c r="O99" s="190"/>
+      <c r="P99" s="190"/>
+    </row>
+    <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D100" s="190"/>
+      <c r="E100" s="190"/>
+      <c r="F100" s="190"/>
+      <c r="G100" s="190"/>
+      <c r="H100" s="190"/>
+      <c r="I100" s="190"/>
+      <c r="J100" s="190"/>
+      <c r="K100" s="190"/>
+      <c r="L100" s="190"/>
+      <c r="M100" s="190"/>
+      <c r="N100" s="190"/>
+      <c r="O100" s="190"/>
+      <c r="P100" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="M1:N1"/>
@@ -9166,17 +9186,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/VERGARA/Mayo/vergara MAYO.xlsx
+++ b/VERGARA/Mayo/vergara MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AAED02-C6CA-4BA8-96CB-0786DCB374B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1780D0F7-E5E1-465B-A27C-B5F88EB2B2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -722,9 +722,6 @@
     <t>Javier Enrique Zambrano</t>
   </si>
   <si>
-    <t>Barbara Fusito y Ezequiel</t>
-  </si>
-  <si>
     <t>Carlos Mehinger Lisa</t>
   </si>
   <si>
@@ -894,6 +891,9 @@
   </si>
   <si>
     <t>HABIA PAGADO LOS 5300, SU DEUDA DEBE ESTAR EN 0</t>
+  </si>
+  <si>
+    <t>Barbara Fucito</t>
   </si>
 </sst>
 </file>
@@ -901,15 +901,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1514,8 +1514,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1525,7 +1525,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1538,8 +1538,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1548,31 +1548,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1583,8 +1583,8 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1605,19 +1605,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1638,35 +1638,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1674,12 +1674,12 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1690,18 +1690,18 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1717,27 +1717,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1747,7 +1747,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1755,30 +1755,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1786,17 +1786,32 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="20" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1825,37 +1840,16 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1863,24 +1857,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1891,9 +1867,33 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2261,20 +2261,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="68" t="s">
         <v>180</v>
@@ -2283,7 +2283,7 @@
       <c r="D1" s="68"/>
       <c r="E1" s="69"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="136" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
       <c r="D2" s="136"/>
       <c r="E2" s="70"/>
     </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="137" t="s">
         <v>213</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E3" s="70"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2314,18 +2314,18 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="199" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="199"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="200"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="193" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="194"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>190</v>
       </c>
@@ -2336,57 +2336,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="202" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="202"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="202"/>
-      <c r="C10" s="202"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="201" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="196" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="196"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="196"/>
+      <c r="C10" s="196"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="195" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="201"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="201"/>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="201"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="201"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="195"/>
+      <c r="C13" s="195"/>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="195"/>
+      <c r="B15" s="195"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="195"/>
+      <c r="B16" s="195"/>
+      <c r="C16" s="195"/>
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>11</v>
       </c>
@@ -2395,7 +2395,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
         <v>37</v>
       </c>
@@ -2404,7 +2404,7 @@
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>188</v>
       </c>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E22" s="90"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>186</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="E23" s="90"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>187</v>
       </c>
@@ -2439,7 +2439,7 @@
       <c r="E24" s="90"/>
       <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="56" t="s">
         <v>38</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="E25" s="91"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>1</v>
       </c>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="33" t="s">
         <v>23</v>
       </c>
@@ -2474,11 +2474,11 @@
       <c r="D27" s="34"/>
       <c r="E27" s="93"/>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="188" t="s">
-        <v>250</v>
-      </c>
-      <c r="B28" s="189"/>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="191" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="192"/>
       <c r="C28" s="5"/>
       <c r="D28" s="184">
         <v>31000</v>
@@ -2487,20 +2487,20 @@
         <v>221</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="188" t="s">
-        <v>252</v>
-      </c>
-      <c r="B29" s="189"/>
+    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="191" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" s="192"/>
       <c r="C29" s="5"/>
       <c r="D29" s="184">
         <v>470000</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
         <v>17</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>501000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
         <v>34</v>
       </c>
@@ -2521,9 +2521,9 @@
       <c r="D31" s="35"/>
       <c r="E31" s="67"/>
     </row>
-    <row r="32" spans="1:7" s="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" s="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="160" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B32" s="154"/>
       <c r="C32" s="54"/>
@@ -2533,18 +2533,18 @@
       <c r="E32" s="118"/>
       <c r="G32" s="159"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="188" t="s">
-        <v>278</v>
-      </c>
-      <c r="B33" s="189"/>
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="191" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" s="192"/>
       <c r="C33" s="54"/>
       <c r="D33" s="186">
         <v>719.9</v>
       </c>
       <c r="E33" s="118"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="26" t="s">
         <v>2</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
         <v>18</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="D35" s="38"/>
       <c r="E35" s="97"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>47</v>
       </c>
@@ -2575,13 +2575,13 @@
         <v>295029.98</v>
       </c>
       <c r="E36" s="120" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G36" s="125"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>22</v>
@@ -2591,10 +2591,10 @@
         <v>26576.33</v>
       </c>
       <c r="E37" s="105" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="str">
         <f>A37</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2611,7 +2611,7 @@
         <v>Debito 12/05</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="str">
         <f>A38</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2628,7 +2628,7 @@
         <v>Debito 12/05</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>3</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>374947.26999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="33" t="s">
         <v>20</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="D41" s="38"/>
       <c r="E41" s="97"/>
     </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>185</v>
       </c>
@@ -2658,9 +2658,9 @@
       <c r="D42" s="117"/>
       <c r="E42" s="103"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2668,23 +2668,23 @@
         <v>50000</v>
       </c>
       <c r="E43" s="103" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="188" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="191" t="s">
         <v>222</v>
       </c>
-      <c r="B44" s="189"/>
+      <c r="B44" s="192"/>
       <c r="C44" s="5"/>
       <c r="D44" s="117">
         <v>81423.929999999993</v>
       </c>
       <c r="E44" s="103" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="26" t="s">
         <v>4</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>131423.93</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>19</v>
       </c>
@@ -2705,36 +2705,36 @@
       <c r="D46" s="37"/>
       <c r="E46" s="99"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="192" t="s">
-        <v>271</v>
-      </c>
-      <c r="B47" s="193"/>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="199" t="s">
+        <v>270</v>
+      </c>
+      <c r="B47" s="200"/>
       <c r="C47" s="65"/>
       <c r="D47" s="117">
         <v>84500</v>
       </c>
       <c r="E47" s="157" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="192" t="s">
-        <v>272</v>
-      </c>
-      <c r="B48" s="193"/>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="199" t="s">
+        <v>271</v>
+      </c>
+      <c r="B48" s="200"/>
       <c r="C48" s="65"/>
       <c r="D48" s="117">
         <v>262099.86</v>
       </c>
       <c r="E48" s="157" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G48" s="140"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="155" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B49" s="156"/>
       <c r="C49" s="65"/>
@@ -2742,12 +2742,12 @@
         <v>36300</v>
       </c>
       <c r="E49" s="158" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="155" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B50" s="156"/>
       <c r="C50" s="65"/>
@@ -2755,51 +2755,51 @@
         <v>25000</v>
       </c>
       <c r="E50" s="158" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="188" t="s">
-        <v>257</v>
-      </c>
-      <c r="B51" s="189"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="191" t="s">
+        <v>256</v>
+      </c>
+      <c r="B51" s="192"/>
       <c r="C51" s="55"/>
       <c r="D51" s="117">
         <v>165000</v>
       </c>
       <c r="E51" s="157" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="188" t="s">
-        <v>281</v>
-      </c>
-      <c r="B52" s="189"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="191" t="s">
+        <v>280</v>
+      </c>
+      <c r="B52" s="192"/>
       <c r="C52" s="55"/>
       <c r="D52" s="117">
         <v>450000</v>
       </c>
       <c r="E52" s="157" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="188" t="s">
-        <v>256</v>
-      </c>
-      <c r="B53" s="189"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="191" t="s">
+        <v>255</v>
+      </c>
+      <c r="B53" s="192"/>
       <c r="C53" s="55"/>
       <c r="D53" s="117">
         <v>230000</v>
       </c>
       <c r="E53" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="143" t="s">
         <v>254</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="143" t="s">
-        <v>255</v>
       </c>
       <c r="B54" s="132"/>
       <c r="C54" s="55"/>
@@ -2807,25 +2807,25 @@
         <v>385000</v>
       </c>
       <c r="E54" s="157" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="188" t="s">
-        <v>282</v>
-      </c>
-      <c r="B55" s="189"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="191" t="s">
+        <v>281</v>
+      </c>
+      <c r="B55" s="192"/>
       <c r="C55" s="55"/>
       <c r="D55" s="117">
         <v>135000</v>
       </c>
       <c r="E55" s="158" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="143" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B56" s="132"/>
       <c r="C56" s="55"/>
@@ -2833,38 +2833,38 @@
         <v>670000</v>
       </c>
       <c r="E56" s="157" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="194" t="s">
-        <v>264</v>
-      </c>
-      <c r="B57" s="195"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="201" t="s">
+        <v>263</v>
+      </c>
+      <c r="B57" s="202"/>
       <c r="C57" s="5"/>
       <c r="D57" s="117">
         <v>110000</v>
       </c>
       <c r="E57" s="158" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="188" t="s">
-        <v>261</v>
-      </c>
-      <c r="B58" s="189"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="191" t="s">
+        <v>260</v>
+      </c>
+      <c r="B58" s="192"/>
       <c r="C58" s="5"/>
       <c r="D58" s="101">
         <v>150000</v>
       </c>
       <c r="E58" s="157" t="s">
-        <v>262</v>
-      </c>
-      <c r="I58" s="188"/>
-      <c r="J58" s="189"/>
-    </row>
-    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+      <c r="I58" s="191"/>
+      <c r="J58" s="192"/>
+    </row>
+    <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
         <v>10</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>2702899.86</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="33" t="s">
         <v>13</v>
       </c>
@@ -2885,7 +2885,7 @@
       <c r="D60" s="28"/>
       <c r="E60" s="99"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>216</v>
       </c>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E61" s="107"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>217</v>
       </c>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E62" s="104"/>
     </row>
-    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="52" t="s">
         <v>17</v>
       </c>
@@ -2920,30 +2920,30 @@
         <v>168465.71000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="90"/>
       <c r="E64" s="109"/>
     </row>
-    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B65" s="29"/>
       <c r="C65" s="29"/>
       <c r="D65" s="110"/>
       <c r="E65" s="142"/>
     </row>
-    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="D66" s="111"/>
       <c r="E66" s="112"/>
       <c r="F66" s="45"/>
       <c r="G66" s="149"/>
     </row>
-    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>14</v>
       </c>
@@ -2956,15 +2956,15 @@
       </c>
       <c r="F67" s="140"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D68" s="111"/>
       <c r="E68" s="111"/>
     </row>
-    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D69" s="111"/>
       <c r="E69" s="111"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>45</v>
       </c>
@@ -2973,27 +2973,27 @@
       <c r="D70" s="114"/>
       <c r="E70" s="115"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="188" t="s">
-        <v>258</v>
-      </c>
-      <c r="B71" s="189"/>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="191" t="s">
+        <v>257</v>
+      </c>
+      <c r="B71" s="192"/>
       <c r="C71" s="5"/>
       <c r="D71" s="101">
         <v>304993.06</v>
       </c>
       <c r="E71" s="98" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="100"/>
       <c r="B72" s="102"/>
       <c r="C72" s="5"/>
       <c r="D72" s="101"/>
       <c r="E72" s="98"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
       <c r="B73" s="49"/>
       <c r="C73" s="49"/>
@@ -3003,19 +3003,19 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="196" t="s">
-        <v>279</v>
-      </c>
-      <c r="B76" s="197"/>
-      <c r="C76" s="197"/>
-      <c r="D76" s="198"/>
+    <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="203" t="s">
+        <v>278</v>
+      </c>
+      <c r="B76" s="204"/>
+      <c r="C76" s="204"/>
+      <c r="D76" s="205"/>
       <c r="E76" s="150"/>
     </row>
-    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>24</v>
       </c>
@@ -3027,8 +3027,8 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="87" t="s">
         <v>15</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>4409241.67</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="87" t="s">
         <v>16</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>4409241.67</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="87" t="s">
         <v>25</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="87" t="s">
         <v>41</v>
       </c>
@@ -3064,15 +3064,15 @@
         <v>304993.06</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="46" t="s">
         <v>36</v>
       </c>
       <c r="B85" s="126"/>
       <c r="C85" s="21"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="30" t="s">
         <v>179</v>
       </c>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C86" s="23"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="22" t="s">
         <v>9</v>
       </c>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C87" s="21"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="22" t="s">
         <v>43</v>
       </c>
@@ -3101,9 +3101,9 @@
       </c>
       <c r="C88" s="21"/>
     </row>
-    <row r="89" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="183" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B89" s="48">
         <f>-28214*2</f>
@@ -3111,16 +3111,16 @@
       </c>
       <c r="C89" s="21"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B90" s="48">
         <v>-89980.82</v>
       </c>
       <c r="C90" s="21"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="121" t="s">
         <v>46</v>
       </c>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C91" s="21"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="41" t="s">
         <v>26</v>
       </c>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="C92" s="21"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="41" t="s">
         <v>218</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C93" s="21"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="41" t="s">
         <v>219</v>
       </c>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C94" s="21"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="25" t="s">
         <v>27</v>
       </c>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="C95" s="21"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="130" t="s">
         <v>10</v>
       </c>
@@ -3180,52 +3180,52 @@
       <c r="C96" s="24"/>
       <c r="D96" s="45"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B97" s="43"/>
       <c r="C97" s="24"/>
       <c r="D97" s="45"/>
       <c r="E97" s="127"/>
       <c r="F97" s="128"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B98" s="43"/>
       <c r="C98" s="24"/>
       <c r="D98" s="45"/>
       <c r="E98" s="127"/>
       <c r="F98" s="128"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="191" t="s">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="198" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="191"/>
-      <c r="C99" s="191"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A100" s="191"/>
-      <c r="B100" s="191"/>
-      <c r="C100" s="191"/>
-    </row>
-    <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="198"/>
+      <c r="C99" s="198"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="198"/>
+      <c r="B100" s="198"/>
+      <c r="C100" s="198"/>
+    </row>
+    <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="54"/>
       <c r="B101" s="145"/>
       <c r="C101" s="36">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="54"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
     </row>
-    <row r="103" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="134"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36">
         <v>61209</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="46" t="s">
         <v>10</v>
       </c>
@@ -3235,46 +3235,39 @@
       </c>
       <c r="C104" s="47"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M105" s="8"/>
     </row>
-    <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="190"/>
-      <c r="B106" s="190"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="190"/>
-      <c r="E106" s="190"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="190"/>
-      <c r="B107" s="190"/>
-      <c r="C107" s="190"/>
-      <c r="D107" s="190"/>
-      <c r="E107" s="190"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A108" s="190"/>
-      <c r="B108" s="190"/>
-      <c r="C108" s="190"/>
-      <c r="D108" s="190"/>
-      <c r="E108" s="190"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A109" s="190"/>
-      <c r="B109" s="190"/>
-      <c r="C109" s="190"/>
-      <c r="D109" s="190"/>
-      <c r="E109" s="190"/>
+    <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="197"/>
+      <c r="B106" s="197"/>
+      <c r="C106" s="197"/>
+      <c r="D106" s="197"/>
+      <c r="E106" s="197"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="197"/>
+      <c r="B107" s="197"/>
+      <c r="C107" s="197"/>
+      <c r="D107" s="197"/>
+      <c r="E107" s="197"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="197"/>
+      <c r="B108" s="197"/>
+      <c r="C108" s="197"/>
+      <c r="D108" s="197"/>
+      <c r="E108" s="197"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="197"/>
+      <c r="B109" s="197"/>
+      <c r="C109" s="197"/>
+      <c r="D109" s="197"/>
+      <c r="E109" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="A106:E109"/>
     <mergeCell ref="A99:C100"/>
@@ -3288,6 +3281,13 @@
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3298,27 +3298,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="11" width="9.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" customWidth="1"/>
-    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3326,10 +3326,10 @@
       <c r="E1" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="203">
+      <c r="F1" s="215">
         <v>2102777.02</v>
       </c>
-      <c r="G1" s="203"/>
+      <c r="G1" s="215"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3337,19 +3337,19 @@
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="205">
+      <c r="M1" s="217">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="217"/>
       <c r="O1" s="144"/>
-      <c r="P1" s="213">
+      <c r="P1" s="222">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="213"/>
+      <c r="Q1" s="222"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3357,31 +3357,31 @@
       <c r="E2" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="204">
+      <c r="F2" s="216">
         <v>568429.56999999995</v>
       </c>
-      <c r="G2" s="204"/>
+      <c r="G2" s="216"/>
       <c r="H2" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I2" s="212">
+        <v>242</v>
+      </c>
+      <c r="I2" s="221">
         <v>1200000</v>
       </c>
-      <c r="J2" s="212"/>
+      <c r="J2" s="221"/>
       <c r="K2" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="212">
+      <c r="M2" s="221">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="212"/>
+      <c r="N2" s="221"/>
       <c r="O2" s="146"/>
-      <c r="P2" s="214"/>
-      <c r="Q2" s="214"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="215" t="s">
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="206" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="122"/>
@@ -3403,7 +3403,7 @@
       <c r="H3" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="218" t="s">
+      <c r="I3" s="212" t="s">
         <v>33</v>
       </c>
       <c r="J3" s="210" t="s">
@@ -3423,28 +3423,28 @@
         <v>182</v>
       </c>
       <c r="O3" s="210" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="206" t="s">
+      <c r="Q3" s="218" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="45"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="216"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="207"/>
       <c r="B4" s="123"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="217"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="209"/>
       <c r="G4" s="211"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="219"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="213"/>
       <c r="J4" s="211"/>
-      <c r="K4" s="220"/>
+      <c r="K4" s="214"/>
       <c r="L4" s="211"/>
       <c r="M4" s="211"/>
       <c r="N4" s="211"/>
@@ -3453,9 +3453,9 @@
         <f>RESUMEN!B8</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q4" s="207"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q4" s="219"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="62"/>
       <c r="B5" s="62" t="s">
         <v>48</v>
@@ -3518,7 +3518,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="62"/>
       <c r="B6" s="62" t="s">
         <v>50</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="S6" s="45"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="62">
         <v>1</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="62">
         <v>2</v>
       </c>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="T8" s="45"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="62">
         <v>3</v>
       </c>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="T9" s="45"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
         <v>4</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
         <v>5</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="62">
         <v>6</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="62">
         <v>7</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="62">
         <v>8</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="62">
         <v>1</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="62">
         <v>1</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="62">
         <v>2</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="62">
         <v>2</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="62">
         <v>3</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>66</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F19" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4442,10 +4442,10 @@
         <v>0.47</v>
       </c>
       <c r="S19" s="49" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="62">
         <v>3</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="62" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F20" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4512,11 +4512,11 @@
         <v>0.48</v>
       </c>
       <c r="S20" s="49" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T20" s="44"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="62">
         <v>4</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>66</v>
       </c>
       <c r="E21" s="63" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="F21" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4583,7 +4583,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
         <v>4</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="62">
         <v>5</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="62">
         <v>5</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="62">
         <v>6</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="62">
         <v>6</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="62">
         <v>7</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>84</v>
       </c>
       <c r="E27" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F27" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4974,7 +4974,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="62">
         <v>7</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62">
         <v>8</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="62">
         <v>8</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F30" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5173,7 +5173,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="62">
         <v>9</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="62">
         <v>9</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="62">
         <v>10</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="62">
         <v>10</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="62">
         <v>11</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="62">
         <v>11</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>102</v>
       </c>
       <c r="E36" s="181" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F36" s="71">
         <v>2.0199999999999999E-2</v>
@@ -5570,7 +5570,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="62">
         <v>12</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="62">
         <v>12</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>106</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F38" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5701,7 +5701,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="62">
         <v>1</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="62">
         <v>1</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="61">
         <v>1</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="62">
         <v>2</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>59</v>
       </c>
       <c r="E42" s="148" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F42" s="79">
         <v>1.3899999999999999E-2</v>
@@ -5969,7 +5969,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="62">
         <v>2</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="62">
         <v>2</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>115</v>
       </c>
       <c r="E44" s="61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F44" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6097,7 +6097,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="62">
         <v>3</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>118</v>
       </c>
       <c r="E45" s="61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F45" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6161,7 +6161,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="62">
         <v>3</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="62">
         <v>3</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>122</v>
       </c>
       <c r="E47" s="78" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F47" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="T47" s="152"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="62">
         <v>4</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="62">
         <v>4</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>115</v>
       </c>
       <c r="E49" s="61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F49" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6430,7 +6430,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="62">
         <v>4</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="62">
         <v>5</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="62">
         <v>5</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="62">
         <v>5</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>132</v>
       </c>
       <c r="E53" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F53" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6693,7 +6693,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="62">
         <v>6</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>82</v>
       </c>
       <c r="D54" s="61" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E54" s="61"/>
       <c r="F54" s="79">
@@ -6758,7 +6758,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="62">
         <v>6</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="62">
         <v>6</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="62">
         <v>7</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="62">
         <v>7</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="62">
         <v>7</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="62">
         <v>8</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="62">
         <v>8</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="62">
         <v>8</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="62">
         <v>9</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="62">
         <v>9</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="62">
         <v>9</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="62">
         <v>10</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="62">
         <v>10</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="62">
         <v>10</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="62">
         <v>11</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="62">
         <v>11</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="62">
         <v>11</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="62"/>
       <c r="B72" s="81" t="s">
         <v>156</v>
@@ -7858,7 +7858,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="62"/>
       <c r="B73" s="81" t="s">
         <v>157</v>
@@ -7918,7 +7918,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="62"/>
       <c r="B74" s="81" t="s">
         <v>158</v>
@@ -7978,7 +7978,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="62"/>
       <c r="B75" s="81" t="s">
         <v>160</v>
@@ -8038,7 +8038,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="62"/>
       <c r="B76" s="81" t="s">
         <v>161</v>
@@ -8101,7 +8101,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="62"/>
       <c r="B77" s="81" t="s">
         <v>162</v>
@@ -8164,7 +8164,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="62"/>
       <c r="B78" s="81" t="s">
         <v>164</v>
@@ -8227,7 +8227,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="62"/>
       <c r="B79" s="81" t="s">
         <v>165</v>
@@ -8289,7 +8289,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="62"/>
       <c r="B80" s="81" t="s">
         <v>166</v>
@@ -8309,11 +8309,11 @@
       <c r="G80" s="72">
         <v>105752.06</v>
       </c>
-      <c r="H80" s="221">
+      <c r="H80" s="188">
         <f>100452.06</f>
         <v>100452.06</v>
       </c>
-      <c r="I80" s="222">
+      <c r="I80" s="189">
         <f t="shared" si="13"/>
         <v>5300</v>
       </c>
@@ -8353,11 +8353,11 @@
         <f t="shared" si="22"/>
         <v>0.06</v>
       </c>
-      <c r="S80" s="223" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S80" s="190" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="62">
         <v>12</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="62">
         <v>12</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="62">
         <v>12</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="62"/>
       <c r="B84" s="80" t="s">
         <v>171</v>
@@ -8606,7 +8606,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="62"/>
       <c r="B85" s="80" t="s">
         <v>172</v>
@@ -8618,7 +8618,7 @@
         <v>115</v>
       </c>
       <c r="E85" s="63" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F85" s="71">
         <v>5.3E-3</v>
@@ -8671,7 +8671,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="62"/>
       <c r="B86" s="80" t="s">
         <v>173</v>
@@ -8736,7 +8736,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="62"/>
       <c r="B87" s="62" t="s">
         <v>174</v>
@@ -8799,7 +8799,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A88" s="62"/>
       <c r="B88" s="62" t="s">
         <v>175</v>
@@ -8861,7 +8861,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="62"/>
       <c r="B89" s="62" t="s">
         <v>176</v>
@@ -8927,7 +8927,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="61"/>
       <c r="B90" s="61" t="s">
         <v>177</v>
@@ -8989,7 +8989,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="62"/>
       <c r="B91" s="147"/>
       <c r="C91" s="147"/>
@@ -9009,7 +9009,7 @@
       <c r="Q91" s="170"/>
       <c r="R91" s="45"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="85"/>
       <c r="B92" s="171"/>
       <c r="C92" s="172"/>
@@ -9064,116 +9064,105 @@
         <v>13568044.699999999</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
     </row>
-    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="190" t="str">
+    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D95" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="190"/>
-      <c r="F95" s="190"/>
-      <c r="G95" s="190"/>
-      <c r="H95" s="190"/>
-      <c r="I95" s="190"/>
-      <c r="J95" s="190"/>
-      <c r="K95" s="190"/>
-      <c r="L95" s="190"/>
-      <c r="M95" s="190"/>
-      <c r="N95" s="190"/>
-      <c r="O95" s="190"/>
-      <c r="P95" s="190"/>
-    </row>
-    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="190"/>
-      <c r="E96" s="190"/>
-      <c r="F96" s="190"/>
-      <c r="G96" s="190"/>
-      <c r="H96" s="190"/>
-      <c r="I96" s="190"/>
-      <c r="J96" s="190"/>
-      <c r="K96" s="190"/>
-      <c r="L96" s="190"/>
-      <c r="M96" s="190"/>
-      <c r="N96" s="190"/>
-      <c r="O96" s="190"/>
-      <c r="P96" s="190"/>
-    </row>
-    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="190"/>
-      <c r="E97" s="190"/>
-      <c r="F97" s="190"/>
-      <c r="G97" s="190"/>
-      <c r="H97" s="190"/>
-      <c r="I97" s="190"/>
-      <c r="J97" s="190"/>
-      <c r="K97" s="190"/>
-      <c r="L97" s="190"/>
-      <c r="M97" s="190"/>
-      <c r="N97" s="190"/>
-      <c r="O97" s="190"/>
-      <c r="P97" s="190"/>
-    </row>
-    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="190"/>
-      <c r="E98" s="190"/>
-      <c r="F98" s="190"/>
-      <c r="G98" s="190"/>
-      <c r="H98" s="190"/>
-      <c r="I98" s="190"/>
-      <c r="J98" s="190"/>
-      <c r="K98" s="190"/>
-      <c r="L98" s="190"/>
-      <c r="M98" s="190"/>
-      <c r="N98" s="190"/>
-      <c r="O98" s="190"/>
-      <c r="P98" s="190"/>
-    </row>
-    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="190"/>
-      <c r="E99" s="190"/>
-      <c r="F99" s="190"/>
-      <c r="G99" s="190"/>
-      <c r="H99" s="190"/>
-      <c r="I99" s="190"/>
-      <c r="J99" s="190"/>
-      <c r="K99" s="190"/>
-      <c r="L99" s="190"/>
-      <c r="M99" s="190"/>
-      <c r="N99" s="190"/>
-      <c r="O99" s="190"/>
-      <c r="P99" s="190"/>
-    </row>
-    <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="190"/>
-      <c r="E100" s="190"/>
-      <c r="F100" s="190"/>
-      <c r="G100" s="190"/>
-      <c r="H100" s="190"/>
-      <c r="I100" s="190"/>
-      <c r="J100" s="190"/>
-      <c r="K100" s="190"/>
-      <c r="L100" s="190"/>
-      <c r="M100" s="190"/>
-      <c r="N100" s="190"/>
-      <c r="O100" s="190"/>
-      <c r="P100" s="190"/>
+      <c r="E95" s="197"/>
+      <c r="F95" s="197"/>
+      <c r="G95" s="197"/>
+      <c r="H95" s="197"/>
+      <c r="I95" s="197"/>
+      <c r="J95" s="197"/>
+      <c r="K95" s="197"/>
+      <c r="L95" s="197"/>
+      <c r="M95" s="197"/>
+      <c r="N95" s="197"/>
+      <c r="O95" s="197"/>
+      <c r="P95" s="197"/>
+    </row>
+    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D96" s="197"/>
+      <c r="E96" s="197"/>
+      <c r="F96" s="197"/>
+      <c r="G96" s="197"/>
+      <c r="H96" s="197"/>
+      <c r="I96" s="197"/>
+      <c r="J96" s="197"/>
+      <c r="K96" s="197"/>
+      <c r="L96" s="197"/>
+      <c r="M96" s="197"/>
+      <c r="N96" s="197"/>
+      <c r="O96" s="197"/>
+      <c r="P96" s="197"/>
+    </row>
+    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="197"/>
+      <c r="E97" s="197"/>
+      <c r="F97" s="197"/>
+      <c r="G97" s="197"/>
+      <c r="H97" s="197"/>
+      <c r="I97" s="197"/>
+      <c r="J97" s="197"/>
+      <c r="K97" s="197"/>
+      <c r="L97" s="197"/>
+      <c r="M97" s="197"/>
+      <c r="N97" s="197"/>
+      <c r="O97" s="197"/>
+      <c r="P97" s="197"/>
+    </row>
+    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D98" s="197"/>
+      <c r="E98" s="197"/>
+      <c r="F98" s="197"/>
+      <c r="G98" s="197"/>
+      <c r="H98" s="197"/>
+      <c r="I98" s="197"/>
+      <c r="J98" s="197"/>
+      <c r="K98" s="197"/>
+      <c r="L98" s="197"/>
+      <c r="M98" s="197"/>
+      <c r="N98" s="197"/>
+      <c r="O98" s="197"/>
+      <c r="P98" s="197"/>
+    </row>
+    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="197"/>
+      <c r="E99" s="197"/>
+      <c r="F99" s="197"/>
+      <c r="G99" s="197"/>
+      <c r="H99" s="197"/>
+      <c r="I99" s="197"/>
+      <c r="J99" s="197"/>
+      <c r="K99" s="197"/>
+      <c r="L99" s="197"/>
+      <c r="M99" s="197"/>
+      <c r="N99" s="197"/>
+      <c r="O99" s="197"/>
+      <c r="P99" s="197"/>
+    </row>
+    <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D100" s="197"/>
+      <c r="E100" s="197"/>
+      <c r="F100" s="197"/>
+      <c r="G100" s="197"/>
+      <c r="H100" s="197"/>
+      <c r="I100" s="197"/>
+      <c r="J100" s="197"/>
+      <c r="K100" s="197"/>
+      <c r="L100" s="197"/>
+      <c r="M100" s="197"/>
+      <c r="N100" s="197"/>
+      <c r="O100" s="197"/>
+      <c r="P100" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="M1:N1"/>
@@ -9186,6 +9175,17 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/VERGARA/Mayo/vergara MAYO.xlsx
+++ b/VERGARA/Mayo/vergara MAYO.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1780D0F7-E5E1-465B-A27C-B5F88EB2B2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E81CBF-F8BD-41EE-9C35-92281B07CBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
+    <sheet name="anotaciones" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$Q$101</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="290">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -601,9 +602,6 @@
   </si>
   <si>
     <t>Micaela Contreras</t>
-  </si>
-  <si>
-    <t>Aranda Jonhatan</t>
   </si>
   <si>
     <t>Dario Javier Flecha</t>
@@ -894,6 +892,12 @@
   </si>
   <si>
     <t>Barbara Fucito</t>
+  </si>
+  <si>
+    <t>LA COCHERA S.S31 DE MICAELA CONTRERAS ESTABA ABONADA EL MES PASADO CON UN MONTO DE 91,358 , SIN EMBARGO ESE MONTO LO PUSIMOS EN LA UF 60 COMO DINERO A FAVOR, CORREGIR ESO</t>
+  </si>
+  <si>
+    <t>AGUSTINA AYELEN MARTINEZ PAGA EK 8D Y LA COCHERA S.S 22, DESDE SIEMPRE LE PONEMOS PAGO EL 8D PERO COMO NO SABIAMOS QUE TAMBIEN PAGA LA COCHERA S.S 22 LA COCHERA LE QUEDABA IMPAGA, RASTREAR LOS PAGOS Y RESTAR LO NECESARIO</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1103,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1163,6 +1167,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1517,7 +1527,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1795,23 +1805,13 @@
     <xf numFmtId="168" fontId="20" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="20" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1840,32 +1840,17 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1882,8 +1867,17 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1894,6 +1888,25 @@
     <xf numFmtId="171" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2295,7 +2308,7 @@
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="137" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C3" s="136"/>
       <c r="D3" s="138" t="s">
@@ -2308,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -2316,14 +2329,14 @@
     </row>
     <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="193" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="193"/>
-      <c r="E5" s="194"/>
+        <v>213</v>
+      </c>
+      <c r="B5" s="204" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="204"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="205"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -2337,49 +2350,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="196" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="196"/>
+      <c r="B8" s="207" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="196"/>
-      <c r="C10" s="196"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="195" t="s">
+      <c r="A13" s="206" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="195"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="195"/>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="195"/>
-      <c r="B15" s="195"/>
-      <c r="C15" s="195"/>
-      <c r="D15" s="195"/>
-      <c r="E15" s="195"/>
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="195"/>
-      <c r="B16" s="195"/>
-      <c r="C16" s="195"/>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2475,29 +2488,29 @@
       <c r="E27" s="93"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="191" t="s">
-        <v>249</v>
-      </c>
-      <c r="B28" s="192"/>
+      <c r="A28" s="193" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" s="194"/>
       <c r="C28" s="5"/>
       <c r="D28" s="184">
         <v>31000</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="191" t="s">
-        <v>251</v>
-      </c>
-      <c r="B29" s="192"/>
+      <c r="A29" s="193" t="s">
+        <v>250</v>
+      </c>
+      <c r="B29" s="194"/>
       <c r="C29" s="5"/>
       <c r="D29" s="184">
         <v>470000</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2523,7 +2536,7 @@
     </row>
     <row r="32" spans="1:7" s="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="160" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B32" s="154"/>
       <c r="C32" s="54"/>
@@ -2534,10 +2547,10 @@
       <c r="G32" s="159"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="191" t="s">
-        <v>277</v>
-      </c>
-      <c r="B33" s="192"/>
+      <c r="A33" s="193" t="s">
+        <v>276</v>
+      </c>
+      <c r="B33" s="194"/>
       <c r="C33" s="54"/>
       <c r="D33" s="186">
         <v>719.9</v>
@@ -2575,13 +2588,13 @@
         <v>295029.98</v>
       </c>
       <c r="E36" s="120" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G36" s="125"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>22</v>
@@ -2591,7 +2604,7 @@
         <v>26576.33</v>
       </c>
       <c r="E37" s="105" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2660,7 +2673,7 @@
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2668,20 +2681,20 @@
         <v>50000</v>
       </c>
       <c r="E43" s="103" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="191" t="s">
-        <v>222</v>
-      </c>
-      <c r="B44" s="192"/>
+      <c r="A44" s="193" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" s="194"/>
       <c r="C44" s="5"/>
       <c r="D44" s="117">
         <v>81423.929999999993</v>
       </c>
       <c r="E44" s="103" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2706,35 +2719,35 @@
       <c r="E46" s="99"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="199" t="s">
-        <v>270</v>
-      </c>
-      <c r="B47" s="200"/>
+      <c r="A47" s="197" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="198"/>
       <c r="C47" s="65"/>
       <c r="D47" s="117">
         <v>84500</v>
       </c>
       <c r="E47" s="157" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="199" t="s">
-        <v>271</v>
-      </c>
-      <c r="B48" s="200"/>
+      <c r="A48" s="197" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48" s="198"/>
       <c r="C48" s="65"/>
       <c r="D48" s="117">
         <v>262099.86</v>
       </c>
       <c r="E48" s="157" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G48" s="140"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="155" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B49" s="156"/>
       <c r="C49" s="65"/>
@@ -2742,12 +2755,12 @@
         <v>36300</v>
       </c>
       <c r="E49" s="158" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="155" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B50" s="156"/>
       <c r="C50" s="65"/>
@@ -2755,51 +2768,51 @@
         <v>25000</v>
       </c>
       <c r="E50" s="158" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="191" t="s">
-        <v>256</v>
-      </c>
-      <c r="B51" s="192"/>
+      <c r="A51" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="B51" s="194"/>
       <c r="C51" s="55"/>
       <c r="D51" s="117">
         <v>165000</v>
       </c>
       <c r="E51" s="157" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="191" t="s">
-        <v>280</v>
-      </c>
-      <c r="B52" s="192"/>
+      <c r="A52" s="193" t="s">
+        <v>279</v>
+      </c>
+      <c r="B52" s="194"/>
       <c r="C52" s="55"/>
       <c r="D52" s="117">
         <v>450000</v>
       </c>
       <c r="E52" s="157" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="191" t="s">
-        <v>255</v>
-      </c>
-      <c r="B53" s="192"/>
+      <c r="A53" s="193" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" s="194"/>
       <c r="C53" s="55"/>
       <c r="D53" s="117">
         <v>230000</v>
       </c>
       <c r="E53" s="157" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="143" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B54" s="132"/>
       <c r="C54" s="55"/>
@@ -2807,25 +2820,25 @@
         <v>385000</v>
       </c>
       <c r="E54" s="157" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="191" t="s">
-        <v>281</v>
-      </c>
-      <c r="B55" s="192"/>
+      <c r="A55" s="193" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" s="194"/>
       <c r="C55" s="55"/>
       <c r="D55" s="117">
         <v>135000</v>
       </c>
       <c r="E55" s="158" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="143" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B56" s="132"/>
       <c r="C56" s="55"/>
@@ -2833,36 +2846,36 @@
         <v>670000</v>
       </c>
       <c r="E56" s="157" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="201" t="s">
-        <v>263</v>
-      </c>
-      <c r="B57" s="202"/>
+      <c r="A57" s="199" t="s">
+        <v>262</v>
+      </c>
+      <c r="B57" s="200"/>
       <c r="C57" s="5"/>
       <c r="D57" s="117">
         <v>110000</v>
       </c>
       <c r="E57" s="158" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="191" t="s">
-        <v>260</v>
-      </c>
-      <c r="B58" s="192"/>
+      <c r="A58" s="193" t="s">
+        <v>259</v>
+      </c>
+      <c r="B58" s="194"/>
       <c r="C58" s="5"/>
       <c r="D58" s="101">
         <v>150000</v>
       </c>
       <c r="E58" s="157" t="s">
-        <v>261</v>
-      </c>
-      <c r="I58" s="191"/>
-      <c r="J58" s="192"/>
+        <v>260</v>
+      </c>
+      <c r="I58" s="193"/>
+      <c r="J58" s="194"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
@@ -2887,7 +2900,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2899,7 +2912,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2929,7 +2942,7 @@
     </row>
     <row r="65" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B65" s="29"/>
       <c r="C65" s="29"/>
@@ -2974,16 +2987,16 @@
       <c r="E70" s="115"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="191" t="s">
-        <v>257</v>
-      </c>
-      <c r="B71" s="192"/>
+      <c r="A71" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="B71" s="194"/>
       <c r="C71" s="5"/>
       <c r="D71" s="101">
         <v>304993.06</v>
       </c>
       <c r="E71" s="98" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3006,12 +3019,12 @@
     <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="203" t="s">
-        <v>278</v>
-      </c>
-      <c r="B76" s="204"/>
-      <c r="C76" s="204"/>
-      <c r="D76" s="205"/>
+      <c r="A76" s="201" t="s">
+        <v>277</v>
+      </c>
+      <c r="B76" s="202"/>
+      <c r="C76" s="202"/>
+      <c r="D76" s="203"/>
       <c r="E76" s="150"/>
     </row>
     <row r="77" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3087,7 +3100,7 @@
       </c>
       <c r="B87" s="42">
         <f>PRORRATEO!H92</f>
-        <v>6635088.2499999981</v>
+        <v>6723784.4099999983</v>
       </c>
       <c r="C87" s="21"/>
     </row>
@@ -3103,7 +3116,7 @@
     </row>
     <row r="89" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B89" s="48">
         <f>-28214*2</f>
@@ -3113,7 +3126,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B90" s="48">
         <v>-89980.82</v>
@@ -3141,7 +3154,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B93" s="48">
         <f>-PRORRATEO!F1</f>
@@ -3151,7 +3164,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B94" s="48">
         <f>-PRORRATEO!F2</f>
@@ -3175,7 +3188,7 @@
       </c>
       <c r="B96" s="131">
         <f>SUM(B86:B95)</f>
-        <v>-408061.46538320422</v>
+        <v>-319365.30538320408</v>
       </c>
       <c r="C96" s="24"/>
       <c r="D96" s="45"/>
@@ -3195,16 +3208,16 @@
       <c r="F98" s="128"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="198" t="s">
+      <c r="A99" s="196" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="198"/>
-      <c r="C99" s="198"/>
+      <c r="B99" s="196"/>
+      <c r="C99" s="196"/>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="198"/>
-      <c r="B100" s="198"/>
-      <c r="C100" s="198"/>
+      <c r="A100" s="196"/>
+      <c r="B100" s="196"/>
+      <c r="C100" s="196"/>
     </row>
     <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="54"/>
@@ -3239,35 +3252,42 @@
       <c r="M105" s="8"/>
     </row>
     <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="197"/>
-      <c r="B106" s="197"/>
-      <c r="C106" s="197"/>
-      <c r="D106" s="197"/>
-      <c r="E106" s="197"/>
+      <c r="A106" s="195"/>
+      <c r="B106" s="195"/>
+      <c r="C106" s="195"/>
+      <c r="D106" s="195"/>
+      <c r="E106" s="195"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="197"/>
-      <c r="B107" s="197"/>
-      <c r="C107" s="197"/>
-      <c r="D107" s="197"/>
-      <c r="E107" s="197"/>
+      <c r="A107" s="195"/>
+      <c r="B107" s="195"/>
+      <c r="C107" s="195"/>
+      <c r="D107" s="195"/>
+      <c r="E107" s="195"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="197"/>
-      <c r="B108" s="197"/>
-      <c r="C108" s="197"/>
-      <c r="D108" s="197"/>
-      <c r="E108" s="197"/>
+      <c r="A108" s="195"/>
+      <c r="B108" s="195"/>
+      <c r="C108" s="195"/>
+      <c r="D108" s="195"/>
+      <c r="E108" s="195"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="197"/>
-      <c r="B109" s="197"/>
-      <c r="C109" s="197"/>
-      <c r="D109" s="197"/>
-      <c r="E109" s="197"/>
+      <c r="A109" s="195"/>
+      <c r="B109" s="195"/>
+      <c r="C109" s="195"/>
+      <c r="D109" s="195"/>
+      <c r="E109" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="A106:E109"/>
     <mergeCell ref="A99:C100"/>
@@ -3281,13 +3301,6 @@
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3326,10 +3339,10 @@
       <c r="E1" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="215">
+      <c r="F1" s="208">
         <v>2102777.02</v>
       </c>
-      <c r="G1" s="215"/>
+      <c r="G1" s="208"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3337,16 +3350,16 @@
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="217">
+      <c r="M1" s="210">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="217"/>
+      <c r="N1" s="210"/>
       <c r="O1" s="144"/>
-      <c r="P1" s="222">
+      <c r="P1" s="218">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="222"/>
+      <c r="Q1" s="218"/>
       <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3357,103 +3370,103 @@
       <c r="E2" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="216">
+      <c r="F2" s="209">
         <v>568429.56999999995</v>
       </c>
-      <c r="G2" s="216"/>
+      <c r="G2" s="209"/>
       <c r="H2" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="I2" s="221">
+        <v>241</v>
+      </c>
+      <c r="I2" s="217">
         <v>1200000</v>
       </c>
-      <c r="J2" s="221"/>
+      <c r="J2" s="217"/>
       <c r="K2" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="221">
+      <c r="M2" s="217">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="217"/>
       <c r="O2" s="146"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="219"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="206" t="s">
+      <c r="A3" s="220" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="122"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="208" t="s">
+      <c r="D3" s="213" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="208" t="s">
+      <c r="E3" s="213" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="208" t="s">
+      <c r="F3" s="213" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="210" t="s">
+      <c r="G3" s="215" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="208" t="s">
+      <c r="H3" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="212" t="s">
+      <c r="I3" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="210" t="s">
+      <c r="J3" s="215" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="210" t="str">
+      <c r="K3" s="215" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="210" t="s">
+      <c r="L3" s="215" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="210" t="s">
+      <c r="M3" s="215" t="s">
         <v>181</v>
       </c>
-      <c r="N3" s="210" t="s">
+      <c r="N3" s="215" t="s">
         <v>182</v>
       </c>
-      <c r="O3" s="210" t="s">
-        <v>241</v>
+      <c r="O3" s="215" t="s">
+        <v>240</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="218" t="s">
+      <c r="Q3" s="211" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="45"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="207"/>
+      <c r="A4" s="221"/>
       <c r="B4" s="123"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="214"/>
-      <c r="L4" s="211"/>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="224"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="216"/>
+      <c r="M4" s="216"/>
+      <c r="N4" s="216"/>
+      <c r="O4" s="216"/>
       <c r="P4" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q4" s="219"/>
+      <c r="Q4" s="212"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="62"/>
@@ -3723,7 +3736,7 @@
         <v>57</v>
       </c>
       <c r="E9" s="181" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F9" s="71">
         <v>2.0199999999999999E-2</v>
@@ -3791,7 +3804,7 @@
         <v>59</v>
       </c>
       <c r="E10" s="148" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F10" s="71">
         <v>1.3899999999999999E-2</v>
@@ -3855,7 +3868,7 @@
         <v>39</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E11" s="148"/>
       <c r="F11" s="71">
@@ -3988,7 +4001,7 @@
         <v>64</v>
       </c>
       <c r="E13" s="181" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F13" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4055,7 +4068,7 @@
         <v>66</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F14" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4122,7 +4135,7 @@
         <v>66</v>
       </c>
       <c r="E15" s="62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F15" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4189,7 +4202,7 @@
         <v>69</v>
       </c>
       <c r="E16" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F16" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4256,7 +4269,7 @@
         <v>66</v>
       </c>
       <c r="E17" s="181" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F17" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4323,7 +4336,7 @@
         <v>66</v>
       </c>
       <c r="E18" s="62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F18" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4390,7 +4403,7 @@
         <v>66</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F19" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4442,7 +4455,7 @@
         <v>0.47</v>
       </c>
       <c r="S19" s="49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4459,7 +4472,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="62" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F20" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4512,7 +4525,7 @@
         <v>0.48</v>
       </c>
       <c r="S20" s="49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T20" s="44"/>
     </row>
@@ -4530,7 +4543,7 @@
         <v>66</v>
       </c>
       <c r="E21" s="63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F21" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4659,7 +4672,7 @@
         <v>66</v>
       </c>
       <c r="E23" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4723,7 +4736,7 @@
         <v>79</v>
       </c>
       <c r="E24" s="148" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="71">
         <v>2.0199999999999999E-2</v>
@@ -4854,7 +4867,7 @@
         <v>66</v>
       </c>
       <c r="E26" s="63" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F26" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4921,7 +4934,7 @@
         <v>84</v>
       </c>
       <c r="E27" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F27" s="71">
         <v>1.3899999999999999E-2</v>
@@ -4988,7 +5001,7 @@
         <v>86</v>
       </c>
       <c r="E28" s="181" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F28" s="71">
         <v>2.0199999999999999E-2</v>
@@ -5120,7 +5133,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F30" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5264,12 +5277,12 @@
         <v>154879</v>
       </c>
       <c r="I32" s="73">
-        <f>G32-H32+91358</f>
-        <v>91357.6</v>
+        <f>G32-H32</f>
+        <v>-0.39999999999417923</v>
       </c>
       <c r="J32" s="73">
         <f t="shared" si="2"/>
-        <v>2740.7280000000001</v>
+        <v>0</v>
       </c>
       <c r="K32" s="74">
         <f t="shared" si="3"/>
@@ -5293,11 +5306,11 @@
       </c>
       <c r="P32" s="75">
         <f t="shared" si="9"/>
-        <v>251178.6</v>
+        <v>157079.6</v>
       </c>
       <c r="Q32" s="76">
         <f t="shared" si="1"/>
-        <v>258713.60000000001</v>
+        <v>161791.6</v>
       </c>
       <c r="R32" s="45">
         <f t="shared" si="8"/>
@@ -5383,7 +5396,7 @@
         <v>98</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F34" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5450,7 +5463,7 @@
         <v>100</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F35" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5517,7 +5530,7 @@
         <v>102</v>
       </c>
       <c r="E36" s="181" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F36" s="71">
         <v>2.0199999999999999E-2</v>
@@ -5525,7 +5538,7 @@
       <c r="G36" s="72">
         <v>88536.639999999999</v>
       </c>
-      <c r="H36" s="124">
+      <c r="H36" s="226">
         <f>150000</f>
         <v>150000</v>
       </c>
@@ -5584,7 +5597,7 @@
         <v>104</v>
       </c>
       <c r="E37" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F37" s="71">
         <v>2.0199999999999999E-2</v>
@@ -5651,7 +5664,7 @@
         <v>106</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F38" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5715,7 +5728,7 @@
         <v>108</v>
       </c>
       <c r="E39" s="63" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F39" s="71">
         <v>1.3899999999999999E-2</v>
@@ -5850,7 +5863,7 @@
         <v>112</v>
       </c>
       <c r="E41" s="181" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F41" s="79">
         <v>2.0199999999999999E-2</v>
@@ -5916,7 +5929,7 @@
         <v>59</v>
       </c>
       <c r="E42" s="148" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F42" s="79">
         <v>1.3899999999999999E-2</v>
@@ -5983,7 +5996,7 @@
         <v>115</v>
       </c>
       <c r="E43" s="78" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F43" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6047,7 +6060,7 @@
         <v>115</v>
       </c>
       <c r="E44" s="61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F44" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6111,7 +6124,7 @@
         <v>118</v>
       </c>
       <c r="E45" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F45" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6175,7 +6188,7 @@
         <v>120</v>
       </c>
       <c r="E46" s="78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F46" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6242,7 +6255,7 @@
         <v>122</v>
       </c>
       <c r="E47" s="78" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F47" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6310,7 +6323,7 @@
         <v>124</v>
       </c>
       <c r="E48" s="135" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F48" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6377,7 +6390,7 @@
         <v>115</v>
       </c>
       <c r="E49" s="61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F49" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6444,7 +6457,7 @@
         <v>115</v>
       </c>
       <c r="E50" s="61" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F50" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6573,7 +6586,7 @@
         <v>130</v>
       </c>
       <c r="E52" s="61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F52" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6640,7 +6653,7 @@
         <v>132</v>
       </c>
       <c r="E53" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F53" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6704,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="D54" s="61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E54" s="61"/>
       <c r="F54" s="79">
@@ -6772,7 +6785,7 @@
         <v>135</v>
       </c>
       <c r="E55" s="61" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F55" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6973,7 +6986,7 @@
         <v>115</v>
       </c>
       <c r="E59" s="148" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F59" s="79">
         <v>3.2000000000000002E-3</v>
@@ -7226,7 +7239,7 @@
         <v>145</v>
       </c>
       <c r="E63" s="181" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F63" s="79">
         <v>2.0000000000000001E-4</v>
@@ -7355,7 +7368,7 @@
         <v>86</v>
       </c>
       <c r="E65" s="181" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F65" s="79">
         <v>2.0000000000000001E-4</v>
@@ -7487,7 +7500,7 @@
         <v>150</v>
       </c>
       <c r="E67" s="61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F67" s="79">
         <v>2.0000000000000001E-4</v>
@@ -7741,7 +7754,7 @@
         <v>66</v>
       </c>
       <c r="E71" s="61" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F71" s="79">
         <v>2.0000000000000001E-4</v>
@@ -7805,7 +7818,7 @@
         <v>66</v>
       </c>
       <c r="E72" s="148" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F72" s="83">
         <v>2.0000000000000001E-4</v>
@@ -8047,7 +8060,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="182" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E76" s="182"/>
       <c r="F76" s="83">
@@ -8239,7 +8252,7 @@
         <v>59</v>
       </c>
       <c r="E79" s="62" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F79" s="83">
         <v>5.3E-3</v>
@@ -8301,7 +8314,7 @@
         <v>167</v>
       </c>
       <c r="E80" s="78" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F80" s="83">
         <v>5.3E-3</v>
@@ -8354,7 +8367,7 @@
         <v>0.06</v>
       </c>
       <c r="S80" s="190" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8367,10 +8380,12 @@
       <c r="C81" s="62">
         <v>7</v>
       </c>
-      <c r="D81" s="82" t="s">
+      <c r="D81" s="182" t="s">
         <v>102</v>
       </c>
-      <c r="E81" s="82"/>
+      <c r="E81" s="181" t="s">
+        <v>233</v>
+      </c>
       <c r="F81" s="83">
         <v>5.3E-3</v>
       </c>
@@ -8618,7 +8633,7 @@
         <v>115</v>
       </c>
       <c r="E85" s="63" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F85" s="71">
         <v>5.3E-3</v>
@@ -8683,7 +8698,7 @@
         <v>79</v>
       </c>
       <c r="E86" s="62" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F86" s="71">
         <v>5.3E-3</v>
@@ -8811,7 +8826,7 @@
         <v>86</v>
       </c>
       <c r="E88" s="63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F88" s="71">
         <v>5.3E-3</v>
@@ -8935,11 +8950,11 @@
       <c r="C90" s="62">
         <v>16</v>
       </c>
-      <c r="D90" s="62" t="s">
+      <c r="D90" s="148" t="s">
         <v>94</v>
       </c>
-      <c r="E90" s="63" t="s">
-        <v>192</v>
+      <c r="E90" s="148" t="s">
+        <v>191</v>
       </c>
       <c r="F90" s="71">
         <v>6.1999999999999998E-3</v>
@@ -8947,14 +8962,17 @@
       <c r="G90" s="161">
         <v>88696.16</v>
       </c>
-      <c r="H90" s="124"/>
+      <c r="H90" s="191">
+        <f>G90</f>
+        <v>88696.16</v>
+      </c>
       <c r="I90" s="162">
         <f t="shared" si="13"/>
-        <v>88696.16</v>
+        <v>0</v>
       </c>
       <c r="J90" s="73">
         <f t="shared" si="15"/>
-        <v>2660.8847999999998</v>
+        <v>0</v>
       </c>
       <c r="K90" s="74">
         <f t="shared" si="16"/>
@@ -8978,11 +8996,11 @@
       </c>
       <c r="P90" s="75">
         <f t="shared" si="21"/>
-        <v>139569.16</v>
+        <v>48212.160000000003</v>
       </c>
       <c r="Q90" s="76">
         <f t="shared" si="14"/>
-        <v>143756.16</v>
+        <v>49658.16</v>
       </c>
       <c r="R90" s="45">
         <f t="shared" si="22"/>
@@ -9025,15 +9043,15 @@
       </c>
       <c r="H92" s="176">
         <f>SUM(H5:H91)</f>
-        <v>6635088.2499999981</v>
+        <v>6723784.4099999983</v>
       </c>
       <c r="I92" s="177">
         <f>SUM(I5:I91)</f>
-        <v>5236183.4499999993</v>
+        <v>5056129.2899999991</v>
       </c>
       <c r="J92" s="178">
         <f t="shared" ref="J92:P92" si="23">SUM(J5:J91)</f>
-        <v>160450.10639999996</v>
+        <v>155048.49359999999</v>
       </c>
       <c r="K92" s="178">
         <f t="shared" si="23"/>
@@ -9057,112 +9075,126 @@
       </c>
       <c r="P92" s="180">
         <f t="shared" si="23"/>
-        <v>13172858.699999997</v>
+        <v>12987402.699999997</v>
       </c>
       <c r="Q92" s="180">
         <f>SUM(Q5:Q91)</f>
-        <v>13568044.699999999</v>
+        <v>13377024.699999997</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
     </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H94" s="125"/>
+    </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="197" t="str">
+      <c r="D95" s="195" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="197"/>
-      <c r="F95" s="197"/>
-      <c r="G95" s="197"/>
-      <c r="H95" s="197"/>
-      <c r="I95" s="197"/>
-      <c r="J95" s="197"/>
-      <c r="K95" s="197"/>
-      <c r="L95" s="197"/>
-      <c r="M95" s="197"/>
-      <c r="N95" s="197"/>
-      <c r="O95" s="197"/>
-      <c r="P95" s="197"/>
+      <c r="E95" s="195"/>
+      <c r="F95" s="195"/>
+      <c r="G95" s="195"/>
+      <c r="H95" s="195"/>
+      <c r="I95" s="195"/>
+      <c r="J95" s="195"/>
+      <c r="K95" s="195"/>
+      <c r="L95" s="195"/>
+      <c r="M95" s="195"/>
+      <c r="N95" s="195"/>
+      <c r="O95" s="195"/>
+      <c r="P95" s="195"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="197"/>
-      <c r="E96" s="197"/>
-      <c r="F96" s="197"/>
-      <c r="G96" s="197"/>
-      <c r="H96" s="197"/>
-      <c r="I96" s="197"/>
-      <c r="J96" s="197"/>
-      <c r="K96" s="197"/>
-      <c r="L96" s="197"/>
-      <c r="M96" s="197"/>
-      <c r="N96" s="197"/>
-      <c r="O96" s="197"/>
-      <c r="P96" s="197"/>
+      <c r="D96" s="195"/>
+      <c r="E96" s="195"/>
+      <c r="F96" s="195"/>
+      <c r="G96" s="195"/>
+      <c r="H96" s="195"/>
+      <c r="I96" s="195"/>
+      <c r="J96" s="195"/>
+      <c r="K96" s="195"/>
+      <c r="L96" s="195"/>
+      <c r="M96" s="195"/>
+      <c r="N96" s="195"/>
+      <c r="O96" s="195"/>
+      <c r="P96" s="195"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="197"/>
-      <c r="E97" s="197"/>
-      <c r="F97" s="197"/>
-      <c r="G97" s="197"/>
-      <c r="H97" s="197"/>
-      <c r="I97" s="197"/>
-      <c r="J97" s="197"/>
-      <c r="K97" s="197"/>
-      <c r="L97" s="197"/>
-      <c r="M97" s="197"/>
-      <c r="N97" s="197"/>
-      <c r="O97" s="197"/>
-      <c r="P97" s="197"/>
+      <c r="D97" s="195"/>
+      <c r="E97" s="195"/>
+      <c r="F97" s="195"/>
+      <c r="G97" s="195"/>
+      <c r="H97" s="195"/>
+      <c r="I97" s="195"/>
+      <c r="J97" s="195"/>
+      <c r="K97" s="195"/>
+      <c r="L97" s="195"/>
+      <c r="M97" s="195"/>
+      <c r="N97" s="195"/>
+      <c r="O97" s="195"/>
+      <c r="P97" s="195"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="197"/>
-      <c r="E98" s="197"/>
-      <c r="F98" s="197"/>
-      <c r="G98" s="197"/>
-      <c r="H98" s="197"/>
-      <c r="I98" s="197"/>
-      <c r="J98" s="197"/>
-      <c r="K98" s="197"/>
-      <c r="L98" s="197"/>
-      <c r="M98" s="197"/>
-      <c r="N98" s="197"/>
-      <c r="O98" s="197"/>
-      <c r="P98" s="197"/>
+      <c r="D98" s="195"/>
+      <c r="E98" s="195"/>
+      <c r="F98" s="195"/>
+      <c r="G98" s="195"/>
+      <c r="H98" s="195"/>
+      <c r="I98" s="195"/>
+      <c r="J98" s="195"/>
+      <c r="K98" s="195"/>
+      <c r="L98" s="195"/>
+      <c r="M98" s="195"/>
+      <c r="N98" s="195"/>
+      <c r="O98" s="195"/>
+      <c r="P98" s="195"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="197"/>
-      <c r="E99" s="197"/>
-      <c r="F99" s="197"/>
-      <c r="G99" s="197"/>
-      <c r="H99" s="197"/>
-      <c r="I99" s="197"/>
-      <c r="J99" s="197"/>
-      <c r="K99" s="197"/>
-      <c r="L99" s="197"/>
-      <c r="M99" s="197"/>
-      <c r="N99" s="197"/>
-      <c r="O99" s="197"/>
-      <c r="P99" s="197"/>
+      <c r="D99" s="195"/>
+      <c r="E99" s="195"/>
+      <c r="F99" s="195"/>
+      <c r="G99" s="195"/>
+      <c r="H99" s="195"/>
+      <c r="I99" s="195"/>
+      <c r="J99" s="195"/>
+      <c r="K99" s="195"/>
+      <c r="L99" s="195"/>
+      <c r="M99" s="195"/>
+      <c r="N99" s="195"/>
+      <c r="O99" s="195"/>
+      <c r="P99" s="195"/>
     </row>
     <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="197"/>
-      <c r="E100" s="197"/>
-      <c r="F100" s="197"/>
-      <c r="G100" s="197"/>
-      <c r="H100" s="197"/>
-      <c r="I100" s="197"/>
-      <c r="J100" s="197"/>
-      <c r="K100" s="197"/>
-      <c r="L100" s="197"/>
-      <c r="M100" s="197"/>
-      <c r="N100" s="197"/>
-      <c r="O100" s="197"/>
-      <c r="P100" s="197"/>
+      <c r="D100" s="195"/>
+      <c r="E100" s="195"/>
+      <c r="F100" s="195"/>
+      <c r="G100" s="195"/>
+      <c r="H100" s="195"/>
+      <c r="I100" s="195"/>
+      <c r="J100" s="195"/>
+      <c r="K100" s="195"/>
+      <c r="L100" s="195"/>
+      <c r="M100" s="195"/>
+      <c r="N100" s="195"/>
+      <c r="O100" s="195"/>
+      <c r="P100" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="M1:N1"/>
@@ -9175,19 +9207,28 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EFBE5D-A085-4352-B83D-558B648684C3}">
+  <dimension ref="D4:D8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="192" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D8" s="49" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>